--- a/AlphaForge_Fineco_Decision_Cockpit.xlsx
+++ b/AlphaForge_Fineco_Decision_Cockpit.xlsx
@@ -597,26 +597,26 @@
         <v>150</v>
       </c>
       <c r="M2" t="n">
-        <v>454.14</v>
+        <v>452.85</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>448 - 460</t>
+          <t>446 - 459</t>
         </is>
       </c>
       <c r="O2" t="n">
-        <v>1893.75</v>
+        <v>1864.01</v>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>1.797 - 1.987</t>
+          <t>1.766 - 1.959</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>2.78</v>
+        <v>1.91</v>
       </c>
       <c r="R2" t="n">
-        <v>11.59</v>
+        <v>7.87</v>
       </c>
       <c r="S2" t="n">
         <v>0</v>
@@ -809,26 +809,26 @@
         <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>5163.21</v>
+        <v>5156.26</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>4.945 - 5.356</t>
+          <t>4.938 - 5.350</t>
         </is>
       </c>
       <c r="O4" t="n">
-        <v>5685.52</v>
+        <v>5654.95</v>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>5.086 - 6.286</t>
+          <t>5.055 - 6.255</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>3.26</v>
+        <v>3.13</v>
       </c>
       <c r="R4" t="n">
-        <v>13.71</v>
+        <v>13.1</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
@@ -915,33 +915,33 @@
         <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>5056.65</v>
+        <v>5052.27</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>4.823 - 5.261</t>
+          <t>4.818 - 5.258</t>
         </is>
       </c>
       <c r="O5" t="n">
-        <v>5230.5</v>
+        <v>5212.38</v>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>4.630 - 5.831</t>
+          <t>4.612 - 5.812</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>1.13</v>
+        <v>1.05</v>
       </c>
       <c r="R5" t="n">
-        <v>4.61</v>
+        <v>4.25</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>Attenzione / pressione negativa</t>
+          <t>Neutro / da monitorare</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -1021,33 +1021,33 @@
         <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>5056.65</v>
+        <v>5052.27</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>4.823 - 5.261</t>
+          <t>4.818 - 5.258</t>
         </is>
       </c>
       <c r="O6" t="n">
-        <v>5230.5</v>
+        <v>5212.38</v>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>4.630 - 5.831</t>
+          <t>4.612 - 5.812</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>1.13</v>
+        <v>1.05</v>
       </c>
       <c r="R6" t="n">
-        <v>4.61</v>
+        <v>4.25</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>Attenzione / pressione negativa</t>
+          <t>Neutro / da monitorare</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -1127,26 +1127,26 @@
         <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>5056.65</v>
+        <v>5052.27</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>4.823 - 5.261</t>
+          <t>4.818 - 5.258</t>
         </is>
       </c>
       <c r="O7" t="n">
-        <v>5230.5</v>
+        <v>5212.38</v>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>4.630 - 5.831</t>
+          <t>4.612 - 5.812</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>1.13</v>
+        <v>1.05</v>
       </c>
       <c r="R7" t="n">
-        <v>4.61</v>
+        <v>4.25</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
@@ -1233,33 +1233,33 @@
         <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>5039.49</v>
+        <v>5043.91</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>4.804 - 5.246</t>
+          <t>4.809 - 5.250</t>
         </is>
       </c>
       <c r="O8" t="n">
-        <v>5159.82</v>
+        <v>5177.95</v>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>4.560 - 5.760</t>
+          <t>4.578 - 5.778</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>0.79</v>
+        <v>0.88</v>
       </c>
       <c r="R8" t="n">
-        <v>3.2</v>
+        <v>3.56</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>Neutro / da monitorare</t>
+          <t>Potenzialmente favorevole</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
@@ -1399,10 +1399,10 @@
         <v>300</v>
       </c>
       <c r="I2" t="n">
-        <v>26282.41</v>
+        <v>26265.45</v>
       </c>
       <c r="J2" t="n">
-        <v>30359.05</v>
+        <v>30262.51</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>

--- a/AlphaForge_Fineco_Decision_Cockpit.xlsx
+++ b/AlphaForge_Fineco_Decision_Cockpit.xlsx
@@ -941,7 +941,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>Neutro / da monitorare</t>
+          <t>Attenzione / pressione negativa</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>Neutro / da monitorare</t>
+          <t>Attenzione / pressione negativa</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">

--- a/AlphaForge_Fineco_Decision_Cockpit.xlsx
+++ b/AlphaForge_Fineco_Decision_Cockpit.xlsx
@@ -597,7 +597,7 @@
         <v>150</v>
       </c>
       <c r="M2" t="n">
-        <v>452.85</v>
+        <v>453.13</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
@@ -605,18 +605,18 @@
         </is>
       </c>
       <c r="O2" t="n">
-        <v>1864.01</v>
+        <v>1870.3</v>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>1.766 - 1.959</t>
+          <t>1.772 - 1.965</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>1.91</v>
+        <v>2.1</v>
       </c>
       <c r="R2" t="n">
-        <v>7.87</v>
+        <v>8.65</v>
       </c>
       <c r="S2" t="n">
         <v>0</v>
@@ -652,7 +652,7 @@
         </is>
       </c>
       <c r="Z2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="3">
@@ -758,7 +758,7 @@
         </is>
       </c>
       <c r="Z3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="4">
@@ -803,32 +803,32 @@
         <v>3.4</v>
       </c>
       <c r="K4" t="n">
-        <v>3.26</v>
+        <v>3.73</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>5156.26</v>
+        <v>5149.34</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>4.938 - 5.350</t>
+          <t>4.930 - 5.344</t>
         </is>
       </c>
       <c r="O4" t="n">
-        <v>5654.95</v>
+        <v>5624.65</v>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>5.055 - 6.255</t>
+          <t>5.025 - 6.225</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>3.13</v>
+        <v>2.99</v>
       </c>
       <c r="R4" t="n">
-        <v>13.1</v>
+        <v>12.49</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
@@ -864,7 +864,7 @@
         </is>
       </c>
       <c r="Z4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5">
@@ -909,25 +909,25 @@
         <v>1.39</v>
       </c>
       <c r="K5" t="n">
-        <v>1.33</v>
+        <v>1.52</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>5052.27</v>
+        <v>5052.34</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>4.818 - 5.258</t>
+          <t>4.819 - 5.258</t>
         </is>
       </c>
       <c r="O5" t="n">
-        <v>5212.38</v>
+        <v>5212.65</v>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>4.612 - 5.812</t>
+          <t>4.613 - 5.813</t>
         </is>
       </c>
       <c r="Q5" t="n">
@@ -970,7 +970,7 @@
         </is>
       </c>
       <c r="Z5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="6">
@@ -1015,25 +1015,25 @@
         <v>1.39</v>
       </c>
       <c r="K6" t="n">
-        <v>1.33</v>
+        <v>1.52</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>5052.27</v>
+        <v>5052.34</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>4.818 - 5.258</t>
+          <t>4.819 - 5.258</t>
         </is>
       </c>
       <c r="O6" t="n">
-        <v>5212.38</v>
+        <v>5212.65</v>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>4.612 - 5.812</t>
+          <t>4.613 - 5.813</t>
         </is>
       </c>
       <c r="Q6" t="n">
@@ -1076,7 +1076,7 @@
         </is>
       </c>
       <c r="Z6" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="7">
@@ -1121,25 +1121,25 @@
         <v>1.39</v>
       </c>
       <c r="K7" t="n">
-        <v>1.33</v>
+        <v>1.52</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>5052.27</v>
+        <v>5052.34</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>4.818 - 5.258</t>
+          <t>4.819 - 5.258</t>
         </is>
       </c>
       <c r="O7" t="n">
-        <v>5212.38</v>
+        <v>5212.65</v>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>4.612 - 5.812</t>
+          <t>4.613 - 5.813</t>
         </is>
       </c>
       <c r="Q7" t="n">
@@ -1182,7 +1182,7 @@
         </is>
       </c>
       <c r="Z7" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="8">
@@ -1227,32 +1227,32 @@
         <v>0.3</v>
       </c>
       <c r="K8" t="n">
-        <v>0.29</v>
+        <v>0.33</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>5043.91</v>
+        <v>5044.7</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>4.809 - 5.250</t>
+          <t>4.810 - 5.251</t>
         </is>
       </c>
       <c r="O8" t="n">
-        <v>5177.95</v>
+        <v>5181.2</v>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>4.578 - 5.778</t>
+          <t>4.581 - 5.781</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="R8" t="n">
-        <v>3.56</v>
+        <v>3.62</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
@@ -1288,7 +1288,7 @@
         </is>
       </c>
       <c r="Z8" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -1375,12 +1375,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -1399,10 +1399,10 @@
         <v>300</v>
       </c>
       <c r="I2" t="n">
-        <v>26265.45</v>
+        <v>26259.81</v>
       </c>
       <c r="J2" t="n">
-        <v>30262.51</v>
+        <v>30242.56</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>

--- a/AlphaForge_Fineco_Decision_Cockpit.xlsx
+++ b/AlphaForge_Fineco_Decision_Cockpit.xlsx
@@ -597,26 +597,26 @@
         <v>150</v>
       </c>
       <c r="M2" t="n">
-        <v>453.13</v>
+        <v>449.12</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>446 - 459</t>
+          <t>442 - 456</t>
         </is>
       </c>
       <c r="O2" t="n">
-        <v>1870.3</v>
+        <v>1780.86</v>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>1.772 - 1.965</t>
+          <t>1.679 - 1.879</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>2.1</v>
+        <v>-0.58</v>
       </c>
       <c r="R2" t="n">
-        <v>8.65</v>
+        <v>-2.31</v>
       </c>
       <c r="S2" t="n">
         <v>0</v>
@@ -809,26 +809,26 @@
         <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>5149.34</v>
+        <v>5148.59</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>4.930 - 5.344</t>
+          <t>4.929 - 5.343</t>
         </is>
       </c>
       <c r="O4" t="n">
-        <v>5624.65</v>
+        <v>5621.4</v>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>5.025 - 6.225</t>
+          <t>5.021 - 6.221</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>2.99</v>
+        <v>2.97</v>
       </c>
       <c r="R4" t="n">
-        <v>12.49</v>
+        <v>12.43</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
@@ -915,26 +915,26 @@
         <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>5052.34</v>
+        <v>5042.74</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>4.819 - 5.258</t>
+          <t>4.807 - 5.249</t>
         </is>
       </c>
       <c r="O5" t="n">
-        <v>5212.65</v>
+        <v>5173.15</v>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>4.613 - 5.813</t>
+          <t>4.573 - 5.773</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>1.05</v>
+        <v>0.85</v>
       </c>
       <c r="R5" t="n">
-        <v>4.25</v>
+        <v>3.46</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
@@ -1021,26 +1021,26 @@
         <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>5052.34</v>
+        <v>5042.74</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>4.819 - 5.258</t>
+          <t>4.807 - 5.249</t>
         </is>
       </c>
       <c r="O6" t="n">
-        <v>5212.65</v>
+        <v>5173.15</v>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>4.613 - 5.813</t>
+          <t>4.573 - 5.773</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>1.05</v>
+        <v>0.85</v>
       </c>
       <c r="R6" t="n">
-        <v>4.25</v>
+        <v>3.46</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
@@ -1127,26 +1127,26 @@
         <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>5052.34</v>
+        <v>5042.74</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>4.819 - 5.258</t>
+          <t>4.807 - 5.249</t>
         </is>
       </c>
       <c r="O7" t="n">
-        <v>5212.65</v>
+        <v>5173.15</v>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>4.613 - 5.813</t>
+          <t>4.573 - 5.773</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>1.05</v>
+        <v>0.85</v>
       </c>
       <c r="R7" t="n">
-        <v>4.25</v>
+        <v>3.46</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
@@ -1233,26 +1233,26 @@
         <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>5044.7</v>
+        <v>5039.49</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>4.810 - 5.251</t>
+          <t>4.804 - 5.246</t>
         </is>
       </c>
       <c r="O8" t="n">
-        <v>5181.2</v>
+        <v>5159.82</v>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>4.581 - 5.781</t>
+          <t>4.560 - 5.760</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>0.89</v>
+        <v>0.79</v>
       </c>
       <c r="R8" t="n">
-        <v>3.62</v>
+        <v>3.2</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
@@ -1399,10 +1399,10 @@
         <v>300</v>
       </c>
       <c r="I2" t="n">
-        <v>26259.81</v>
+        <v>26221.04</v>
       </c>
       <c r="J2" t="n">
-        <v>30242.56</v>
+        <v>30009.99</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>

--- a/AlphaForge_Fineco_Decision_Cockpit.xlsx
+++ b/AlphaForge_Fineco_Decision_Cockpit.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z8"/>
+  <dimension ref="A1:AI8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -430,122 +430,167 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
+          <t>Nome Strumento</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
           <t>Tipo</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Ruolo</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Categoria</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Data sottoscrizione</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Giorni da inizio</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Importo iniziale EUR</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>PAC mensile EUR</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>Rate PAC stimate versate</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
         <is>
           <t>Capitale versato EUR</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>Controvalore attuale EUR</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
         <is>
           <t>Valore attuale EUR</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>Margine lordo EUR</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>Costo maturato stimato EUR</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>Bollo sottratto EUR</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
         <is>
           <t>Margine netto EUR</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>Margine netto %</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>Costo annuo %</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>Costo maturato stimato EUR</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>PAC mensile EUR</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>Rendimento atteso netto 3M %</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>Rendimento atteso netto 1Y %</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
         <is>
           <t>Proiezione 3M base EUR</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>Range 3M prudente EUR</t>
-        </is>
-      </c>
-      <c r="O1" t="inlineStr">
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>Guadagno stimato 3M EUR</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
         <is>
           <t>Proiezione 1Y base EUR</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
-        <is>
-          <t>Range 1Y prudente EUR</t>
-        </is>
-      </c>
-      <c r="Q1" t="inlineStr">
-        <is>
-          <t>Rendimento atteso netto 3M %</t>
-        </is>
-      </c>
-      <c r="R1" t="inlineStr">
-        <is>
-          <t>Rendimento atteso netto 1Y %</t>
-        </is>
-      </c>
-      <c r="S1" t="inlineStr">
-        <is>
-          <t>Proxy return da inizio %</t>
-        </is>
-      </c>
-      <c r="T1" t="inlineStr">
-        <is>
-          <t>News bias</t>
-        </is>
-      </c>
-      <c r="U1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>Guadagno stimato 1Y EUR</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>Trend proxy</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
+        <is>
+          <t>Proxy usato</t>
+        </is>
+      </c>
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t>Fonte valore</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
+        <is>
+          <t>Fonte dato proxy</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr">
         <is>
           <t>Decisione pratica</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>Motivo</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>Quando valutare switch</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
-        <is>
-          <t>Fonte valore</t>
-        </is>
-      </c>
-      <c r="Y1" t="inlineStr">
-        <is>
-          <t>Data valore Fineco</t>
-        </is>
-      </c>
-      <c r="Z1" t="inlineStr">
-        <is>
-          <t>Giorni da inizio</t>
+      <c r="AH1" t="inlineStr">
+        <is>
+          <t>Nota costi</t>
+        </is>
+      </c>
+      <c r="AI1" t="inlineStr">
+        <is>
+          <t>Aggiornato Roma</t>
         </is>
       </c>
     </row>
@@ -562,97 +607,130 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
+          <t>Sustainable Future Connectivity FAM Fund</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
           <t>PAC</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>Satellite tematico</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>Tecnologia e AI</t>
         </is>
       </c>
-      <c r="F2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G2" t="n">
-        <v>0</v>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>1.8</v>
+        <v>150</v>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L2" t="n">
         <v>150</v>
       </c>
       <c r="M2" t="n">
-        <v>449.12</v>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>442 - 456</t>
-        </is>
+        <v>137.53</v>
+      </c>
+      <c r="N2" t="n">
+        <v>137.53</v>
       </c>
       <c r="O2" t="n">
-        <v>1780.86</v>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>1.679 - 1.879</t>
-        </is>
+        <v>-12.41</v>
+      </c>
+      <c r="P2" t="n">
+        <v>0.07000000000000001</v>
       </c>
       <c r="Q2" t="n">
-        <v>-0.58</v>
+        <v>6</v>
       </c>
       <c r="R2" t="n">
-        <v>-2.31</v>
+        <v>-18.47</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
-      </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>Neutro / da monitorare</t>
-        </is>
-      </c>
-      <c r="U2" t="inlineStr">
-        <is>
-          <t>Tieni / attendi dati reali</t>
-        </is>
-      </c>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t>Portafoglio appena partito: ora serve verificare esecuzione, quote e primo NAV.</t>
-        </is>
-      </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>Valuta switch solo se a 6-12 mesi resta sotto benchmark o cambia il ruolo nel portafoglio.</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>PAC non ancora valorizzato</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
-        </is>
+        <v>-12.31</v>
+      </c>
+      <c r="T2" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="U2" t="n">
+        <v>4.22</v>
+      </c>
+      <c r="V2" t="n">
+        <v>18</v>
+      </c>
+      <c r="W2" t="n">
+        <v>599.62</v>
+      </c>
+      <c r="X2" t="n">
+        <v>-6.38</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>2106.35</v>
       </c>
       <c r="Z2" t="n">
-        <v>8</v>
+        <v>150.35</v>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>Pressione breve</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>WCLD.MI</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Proxy live automatico</t>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>Yahoo/yfinance</t>
+        </is>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>Tieni / monitora</t>
+        </is>
+      </c>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>Appena sottoscritto: ora la priorita' e' leggere correttamente controvalore, costi e primo andamento.</t>
+        </is>
+      </c>
+      <c r="AG2" t="inlineStr">
+        <is>
+          <t>Rivaluta solo dopo 3-6 mesi di dati reali, meglio 12 mesi.</t>
+        </is>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>Proxy di mercato: sottratto costo annuo maturato stimato + bollo una tantum.</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>2026-09-09T12:34:40+02:00</t>
+        </is>
       </c>
     </row>
     <row r="3">
@@ -668,97 +746,130 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
+          <t>FAM MSCI Emerging Markets Index Fund</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
           <t>PAC</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>Satellite geografico</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>Emerging Markets</t>
         </is>
       </c>
-      <c r="F3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G3" t="n">
-        <v>0</v>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>0.3</v>
+        <v>150</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L3" t="n">
         <v>150</v>
       </c>
       <c r="M3" t="n">
-        <v>455.62</v>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>449 - 461</t>
-        </is>
+        <v>152.81</v>
+      </c>
+      <c r="N3" t="n">
+        <v>152.81</v>
       </c>
       <c r="O3" t="n">
-        <v>1928.46</v>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>1.833 - 2.021</t>
-        </is>
+        <v>2.82</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0.01</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.78</v>
+        <v>6</v>
       </c>
       <c r="R3" t="n">
-        <v>16</v>
+        <v>-3.19</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>Neutro / da monitorare</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>Tieni / attendi dati reali</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>Portafoglio appena partito: ora serve verificare esecuzione, quote e primo NAV.</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>Valuta switch solo se a 6-12 mesi resta sotto benchmark o cambia il ruolo nel portafoglio.</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>PAC non ancora valorizzato</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
-        </is>
+        <v>-2.13</v>
+      </c>
+      <c r="T3" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="U3" t="n">
+        <v>4.22</v>
+      </c>
+      <c r="V3" t="n">
+        <v>18</v>
+      </c>
+      <c r="W3" t="n">
+        <v>615.54</v>
+      </c>
+      <c r="X3" t="n">
+        <v>9.539999999999999</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>2124.38</v>
       </c>
       <c r="Z3" t="n">
-        <v>8</v>
+        <v>168.38</v>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>Rimbalzo breve</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>EIMI.MI</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Proxy live automatico</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>Yahoo/yfinance</t>
+        </is>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>Tieni / monitora</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>Appena sottoscritto: ora la priorita' e' leggere correttamente controvalore, costi e primo andamento.</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t>Rivaluta solo dopo 3-6 mesi di dati reali, meglio 12 mesi.</t>
+        </is>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>Proxy di mercato: sottratto costo annuo maturato stimato + bollo una tantum.</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>2026-09-09T12:34:40+02:00</t>
+        </is>
       </c>
     </row>
     <row r="4">
@@ -774,97 +885,130 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
+          <t>Core Dividend</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
           <t>Una tantum</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>Satellite income</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>Dividend globale</t>
         </is>
       </c>
-      <c r="F4" t="n">
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="H4" t="n">
+        <v>9</v>
+      </c>
+      <c r="I4" t="n">
         <v>5000</v>
       </c>
-      <c r="G4" t="n">
+      <c r="J4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" t="n">
         <v>5000</v>
       </c>
-      <c r="H4" t="n">
-        <v>-6</v>
-      </c>
-      <c r="I4" t="n">
-        <v>-0.12</v>
-      </c>
-      <c r="J4" t="n">
+      <c r="M4" t="n">
+        <v>4986.59</v>
+      </c>
+      <c r="N4" t="n">
+        <v>4986.59</v>
+      </c>
+      <c r="O4" t="n">
+        <v>-9.210000000000001</v>
+      </c>
+      <c r="P4" t="n">
+        <v>4.19</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>6</v>
+      </c>
+      <c r="R4" t="n">
+        <v>-19.41</v>
+      </c>
+      <c r="S4" t="n">
+        <v>-0.39</v>
+      </c>
+      <c r="T4" t="n">
         <v>3.4</v>
       </c>
-      <c r="K4" t="n">
-        <v>3.73</v>
-      </c>
-      <c r="L4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M4" t="n">
-        <v>5148.59</v>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>4.929 - 5.343</t>
-        </is>
-      </c>
-      <c r="O4" t="n">
-        <v>5621.4</v>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>5.021 - 6.221</t>
-        </is>
-      </c>
-      <c r="Q4" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="R4" t="n">
-        <v>12.43</v>
-      </c>
-      <c r="S4" t="n">
-        <v>0</v>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>Neutro / da monitorare</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>Tieni ora, ma sotto esame costi</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>Troppo presto per chiudere: prima controlla NAV reale e confronto a 3-6 mesi.</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>Valuta switch se tra 6-12 mesi rende meno del proxy dividend/global dopo costi.</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>Fineco manuale</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
-        </is>
+      <c r="U4" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="V4" t="n">
+        <v>12.91</v>
+      </c>
+      <c r="W4" t="n">
+        <v>5140.24</v>
+      </c>
+      <c r="X4" t="n">
+        <v>134.24</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>5630.16</v>
       </c>
       <c r="Z4" t="n">
-        <v>8</v>
+        <v>624.16</v>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>Laterale</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>VHYL.MI</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Proxy live automatico</t>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t>Yahoo/yfinance</t>
+        </is>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>Tieni ora, sotto esame costi</t>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>Portafoglio appena partito: troppo presto per chiudere, ma il costo alto va verificato.</t>
+        </is>
+      </c>
+      <c r="AG4" t="inlineStr">
+        <is>
+          <t>Valuta switch se tra 6-12 mesi resta sotto un'alternativa dividend/global meno costosa.</t>
+        </is>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>Proxy di mercato: sottratto costo annuo maturato stimato + bollo una tantum.</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>2026-09-09T12:34:40+02:00</t>
+        </is>
       </c>
     </row>
     <row r="5">
@@ -880,97 +1024,130 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
+          <t>Fineco AM Passive Underlyings 7</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
           <t>Una tantum</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>Core gestito</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t>Multi asset</t>
         </is>
       </c>
-      <c r="F5" t="n">
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="H5" t="n">
+        <v>9</v>
+      </c>
+      <c r="I5" t="n">
         <v>5000</v>
       </c>
-      <c r="G5" t="n">
+      <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" t="n">
         <v>5000</v>
       </c>
-      <c r="H5" t="n">
-        <v>-6</v>
-      </c>
-      <c r="I5" t="n">
-        <v>-0.12</v>
-      </c>
-      <c r="J5" t="n">
+      <c r="M5" t="n">
+        <v>4983.3</v>
+      </c>
+      <c r="N5" t="n">
+        <v>4983.3</v>
+      </c>
+      <c r="O5" t="n">
+        <v>-14.99</v>
+      </c>
+      <c r="P5" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>6</v>
+      </c>
+      <c r="R5" t="n">
+        <v>-22.7</v>
+      </c>
+      <c r="S5" t="n">
+        <v>-0.45</v>
+      </c>
+      <c r="T5" t="n">
         <v>1.39</v>
       </c>
-      <c r="K5" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="L5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M5" t="n">
-        <v>5042.74</v>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>4.807 - 5.249</t>
-        </is>
-      </c>
-      <c r="O5" t="n">
-        <v>5173.15</v>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>4.573 - 5.773</t>
-        </is>
-      </c>
-      <c r="Q5" t="n">
-        <v>0.85</v>
-      </c>
-      <c r="R5" t="n">
-        <v>3.46</v>
-      </c>
-      <c r="S5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>Attenzione / pressione negativa</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>Tieni / attendi dati reali</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>Portafoglio appena partito: ora serve verificare esecuzione, quote e primo NAV.</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>Valuta switch solo se a 6-12 mesi resta sotto benchmark o cambia il ruolo nel portafoglio.</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>Fineco manuale</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
-        </is>
+      <c r="U5" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="V5" t="n">
+        <v>7.85</v>
+      </c>
+      <c r="W5" t="n">
+        <v>5078.31</v>
+      </c>
+      <c r="X5" t="n">
+        <v>72.31</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>5374.33</v>
       </c>
       <c r="Z5" t="n">
-        <v>8</v>
+        <v>368.33</v>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>Laterale</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>SWDA.MI</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Proxy live automatico</t>
+        </is>
+      </c>
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t>Yahoo/yfinance</t>
+        </is>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>Tieni / monitora</t>
+        </is>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>Appena sottoscritto: ora la priorita' e' leggere correttamente controvalore, costi e primo andamento.</t>
+        </is>
+      </c>
+      <c r="AG5" t="inlineStr">
+        <is>
+          <t>Rivaluta solo dopo 3-6 mesi di dati reali, meglio 12 mesi.</t>
+        </is>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>Proxy di mercato: sottratto costo annuo maturato stimato + bollo una tantum.</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>2026-09-09T12:34:40+02:00</t>
+        </is>
       </c>
     </row>
     <row r="6">
@@ -986,97 +1163,130 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
+          <t>Fineco AM Passive Underlyings 6</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
           <t>Una tantum</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>Core gestito</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>Multi asset prudente</t>
         </is>
       </c>
-      <c r="F6" t="n">
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="H6" t="n">
+        <v>9</v>
+      </c>
+      <c r="I6" t="n">
         <v>5000</v>
       </c>
-      <c r="G6" t="n">
+      <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" t="n">
         <v>5000</v>
       </c>
-      <c r="H6" t="n">
-        <v>-6</v>
-      </c>
-      <c r="I6" t="n">
-        <v>-0.12</v>
-      </c>
-      <c r="J6" t="n">
+      <c r="M6" t="n">
+        <v>4983.3</v>
+      </c>
+      <c r="N6" t="n">
+        <v>4983.3</v>
+      </c>
+      <c r="O6" t="n">
+        <v>-14.99</v>
+      </c>
+      <c r="P6" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>6</v>
+      </c>
+      <c r="R6" t="n">
+        <v>-22.7</v>
+      </c>
+      <c r="S6" t="n">
+        <v>-0.45</v>
+      </c>
+      <c r="T6" t="n">
         <v>1.39</v>
       </c>
-      <c r="K6" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="L6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M6" t="n">
-        <v>5042.74</v>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>4.807 - 5.249</t>
-        </is>
-      </c>
-      <c r="O6" t="n">
-        <v>5173.15</v>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>4.573 - 5.773</t>
-        </is>
-      </c>
-      <c r="Q6" t="n">
-        <v>0.85</v>
-      </c>
-      <c r="R6" t="n">
-        <v>3.46</v>
-      </c>
-      <c r="S6" t="n">
-        <v>0</v>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>Attenzione / pressione negativa</t>
-        </is>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>Tieni / attendi dati reali</t>
-        </is>
-      </c>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>Portafoglio appena partito: ora serve verificare esecuzione, quote e primo NAV.</t>
-        </is>
-      </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>Valuta switch solo se a 6-12 mesi resta sotto benchmark o cambia il ruolo nel portafoglio.</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>Fineco manuale</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
-        </is>
+      <c r="U6" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="V6" t="n">
+        <v>7.85</v>
+      </c>
+      <c r="W6" t="n">
+        <v>5078.31</v>
+      </c>
+      <c r="X6" t="n">
+        <v>72.31</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>5374.33</v>
       </c>
       <c r="Z6" t="n">
-        <v>8</v>
+        <v>368.33</v>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>Laterale</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>SWDA.MI</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Proxy live automatico</t>
+        </is>
+      </c>
+      <c r="AD6" t="inlineStr">
+        <is>
+          <t>Yahoo/yfinance</t>
+        </is>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t>Tieni / monitora</t>
+        </is>
+      </c>
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>Appena sottoscritto: ora la priorita' e' leggere correttamente controvalore, costi e primo andamento.</t>
+        </is>
+      </c>
+      <c r="AG6" t="inlineStr">
+        <is>
+          <t>Rivaluta solo dopo 3-6 mesi di dati reali, meglio 12 mesi.</t>
+        </is>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>Proxy di mercato: sottratto costo annuo maturato stimato + bollo una tantum.</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>2026-09-09T12:34:40+02:00</t>
+        </is>
       </c>
     </row>
     <row r="7">
@@ -1092,97 +1302,130 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
+          <t>Fineco AM Passive Underlyings 8</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
           <t>Una tantum</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>Core gestito</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t>Multi asset crescita</t>
         </is>
       </c>
-      <c r="F7" t="n">
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="H7" t="n">
+        <v>9</v>
+      </c>
+      <c r="I7" t="n">
         <v>5000</v>
       </c>
-      <c r="G7" t="n">
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
         <v>5000</v>
       </c>
-      <c r="H7" t="n">
-        <v>-6</v>
-      </c>
-      <c r="I7" t="n">
-        <v>-0.12</v>
-      </c>
-      <c r="J7" t="n">
+      <c r="M7" t="n">
+        <v>4983.3</v>
+      </c>
+      <c r="N7" t="n">
+        <v>4983.3</v>
+      </c>
+      <c r="O7" t="n">
+        <v>-14.99</v>
+      </c>
+      <c r="P7" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>6</v>
+      </c>
+      <c r="R7" t="n">
+        <v>-22.7</v>
+      </c>
+      <c r="S7" t="n">
+        <v>-0.45</v>
+      </c>
+      <c r="T7" t="n">
         <v>1.39</v>
       </c>
-      <c r="K7" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="L7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M7" t="n">
-        <v>5042.74</v>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>4.807 - 5.249</t>
-        </is>
-      </c>
-      <c r="O7" t="n">
-        <v>5173.15</v>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>4.573 - 5.773</t>
-        </is>
-      </c>
-      <c r="Q7" t="n">
-        <v>0.85</v>
-      </c>
-      <c r="R7" t="n">
-        <v>3.46</v>
-      </c>
-      <c r="S7" t="n">
-        <v>0</v>
-      </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>Attenzione / pressione negativa</t>
-        </is>
-      </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>Tieni / attendi dati reali</t>
-        </is>
-      </c>
-      <c r="V7" t="inlineStr">
-        <is>
-          <t>Portafoglio appena partito: ora serve verificare esecuzione, quote e primo NAV.</t>
-        </is>
-      </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>Valuta switch solo se a 6-12 mesi resta sotto benchmark o cambia il ruolo nel portafoglio.</t>
-        </is>
-      </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>Fineco manuale</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
-        </is>
+      <c r="U7" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="V7" t="n">
+        <v>7.85</v>
+      </c>
+      <c r="W7" t="n">
+        <v>5078.31</v>
+      </c>
+      <c r="X7" t="n">
+        <v>72.31</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>5374.33</v>
       </c>
       <c r="Z7" t="n">
-        <v>8</v>
+        <v>368.33</v>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>Laterale</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>SWDA.MI</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Proxy live automatico</t>
+        </is>
+      </c>
+      <c r="AD7" t="inlineStr">
+        <is>
+          <t>Yahoo/yfinance</t>
+        </is>
+      </c>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t>Tieni / monitora</t>
+        </is>
+      </c>
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t>Appena sottoscritto: ora la priorita' e' leggere correttamente controvalore, costi e primo andamento.</t>
+        </is>
+      </c>
+      <c r="AG7" t="inlineStr">
+        <is>
+          <t>Rivaluta solo dopo 3-6 mesi di dati reali, meglio 12 mesi.</t>
+        </is>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>Proxy di mercato: sottratto costo annuo maturato stimato + bollo una tantum.</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>2026-09-09T12:34:40+02:00</t>
+        </is>
       </c>
     </row>
     <row r="8">
@@ -1198,97 +1441,130 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
+          <t>Fidelity Euro 50 Index Fund</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
           <t>Una tantum</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>Satellite Europa</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>Europa</t>
         </is>
       </c>
-      <c r="F8" t="n">
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="H8" t="n">
+        <v>9</v>
+      </c>
+      <c r="I8" t="n">
         <v>5000</v>
       </c>
-      <c r="G8" t="n">
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="n">
         <v>5000</v>
       </c>
-      <c r="H8" t="n">
-        <v>-6</v>
-      </c>
-      <c r="I8" t="n">
-        <v>-0.12</v>
-      </c>
-      <c r="J8" t="n">
+      <c r="M8" t="n">
+        <v>4937.29</v>
+      </c>
+      <c r="N8" t="n">
+        <v>4937.29</v>
+      </c>
+      <c r="O8" t="n">
+        <v>-62.34</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>6</v>
+      </c>
+      <c r="R8" t="n">
+        <v>-68.70999999999999</v>
+      </c>
+      <c r="S8" t="n">
+        <v>-1.37</v>
+      </c>
+      <c r="T8" t="n">
         <v>0.3</v>
       </c>
-      <c r="K8" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="L8" t="n">
-        <v>0</v>
-      </c>
-      <c r="M8" t="n">
-        <v>5039.49</v>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>4.804 - 5.246</t>
-        </is>
-      </c>
-      <c r="O8" t="n">
-        <v>5159.82</v>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>4.560 - 5.760</t>
-        </is>
-      </c>
-      <c r="Q8" t="n">
-        <v>0.79</v>
-      </c>
-      <c r="R8" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="S8" t="n">
-        <v>0</v>
-      </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>Potenzialmente favorevole</t>
-        </is>
-      </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>Tieni / attendi dati reali</t>
-        </is>
-      </c>
-      <c r="V8" t="inlineStr">
-        <is>
-          <t>Portafoglio appena partito: ora serve verificare esecuzione, quote e primo NAV.</t>
-        </is>
-      </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>Valuta switch solo se a 6-12 mesi resta sotto benchmark o cambia il ruolo nel portafoglio.</t>
-        </is>
-      </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>Fineco manuale</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
-        </is>
+      <c r="U8" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="V8" t="n">
+        <v>4.99</v>
+      </c>
+      <c r="W8" t="n">
+        <v>4997.74</v>
+      </c>
+      <c r="X8" t="n">
+        <v>-8.26</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>5183.57</v>
       </c>
       <c r="Z8" t="n">
-        <v>8</v>
+        <v>177.57</v>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>Pressione breve</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>EXSA.DE</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Proxy live automatico</t>
+        </is>
+      </c>
+      <c r="AD8" t="inlineStr">
+        <is>
+          <t>Yahoo/yfinance</t>
+        </is>
+      </c>
+      <c r="AE8" t="inlineStr">
+        <is>
+          <t>Tieni / monitora</t>
+        </is>
+      </c>
+      <c r="AF8" t="inlineStr">
+        <is>
+          <t>Appena sottoscritto: ora la priorita' e' leggere correttamente controvalore, costi e primo andamento.</t>
+        </is>
+      </c>
+      <c r="AG8" t="inlineStr">
+        <is>
+          <t>Rivaluta solo dopo 3-6 mesi di dati reali, meglio 12 mesi.</t>
+        </is>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>Proxy di mercato: sottratto costo annuo maturato stimato + bollo una tantum.</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>2026-09-09T12:34:40+02:00</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -1302,7 +1578,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L2"/>
+  <dimension ref="A1:P2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1313,55 +1589,75 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
+          <t>generated_at_rome</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
           <t>data_analisi</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>latest_proxy_date</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>investito_iniziale_eur</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>pac_mensile_eur</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
         <is>
           <t>capitale_versato_eur</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>controvalore_attuale_eur</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
         <is>
           <t>valore_attuale_eur</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>margine_netto_eur</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>margine_netto_pct</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>pac_mensile_eur</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>proiezione_3m_base_eur</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>proiezione_1y_base_eur</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>fonte_prevalente</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
         <is>
           <t>decisione_sintesi</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>messaggio</t>
         </is>
@@ -1370,48 +1666,64 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AlphaForge v10 Decision Cockpit</t>
+          <t>AlphaForge v11 Live Value Cockpit</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09T12:34:40+02:00</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="D2" t="n">
-        <v>25000</v>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
       </c>
       <c r="E2" t="n">
         <v>25000</v>
       </c>
       <c r="F2" t="n">
-        <v>-30</v>
+        <v>300</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.12</v>
+        <v>25300</v>
       </c>
       <c r="H2" t="n">
-        <v>300</v>
+        <v>25164.12</v>
       </c>
       <c r="I2" t="n">
-        <v>26221.04</v>
+        <v>25164.12</v>
       </c>
       <c r="J2" t="n">
-        <v>30009.99</v>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>Tieni: portafoglio troppo recente, ora serve solo controllo dati e NAV</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>Per i fondi comuni il NAV ufficiale non e' real-time. Il margine esatto richiede il controvalore Fineco aggiornato in data/fineco_actual_values.csv.</t>
+        <v>-177.88</v>
+      </c>
+      <c r="K2" t="n">
+        <v>-0.7</v>
+      </c>
+      <c r="L2" t="n">
+        <v>26588.07</v>
+      </c>
+      <c r="M2" t="n">
+        <v>31167.45</v>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>Fineco manuale se compilato; altrimenti proxy live automatico</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>Tieni: controlla soprattutto i costi elevati</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>Streamlit aggiorna dati/proxy all'apertura. Il controvalore Fineco esatto richiede export o inserimento dei valori reali; il proxy live e' una stima di mercato.</t>
         </is>
       </c>
     </row>

--- a/AlphaForge_Fineco_Decision_Cockpit.xlsx
+++ b/AlphaForge_Fineco_Decision_Cockpit.xlsx
@@ -646,13 +646,13 @@
         <v>150</v>
       </c>
       <c r="M2" t="n">
-        <v>137.53</v>
+        <v>136.46</v>
       </c>
       <c r="N2" t="n">
-        <v>137.53</v>
+        <v>136.46</v>
       </c>
       <c r="O2" t="n">
-        <v>-12.41</v>
+        <v>-13.48</v>
       </c>
       <c r="P2" t="n">
         <v>0.07000000000000001</v>
@@ -661,10 +661,10 @@
         <v>6</v>
       </c>
       <c r="R2" t="n">
-        <v>-18.47</v>
+        <v>-19.54</v>
       </c>
       <c r="S2" t="n">
-        <v>-12.31</v>
+        <v>-13.03</v>
       </c>
       <c r="T2" t="n">
         <v>1.8</v>
@@ -676,16 +676,16 @@
         <v>18</v>
       </c>
       <c r="W2" t="n">
-        <v>599.62</v>
+        <v>598.5</v>
       </c>
       <c r="X2" t="n">
-        <v>-6.38</v>
+        <v>-7.5</v>
       </c>
       <c r="Y2" t="n">
-        <v>2106.35</v>
+        <v>2105.08</v>
       </c>
       <c r="Z2" t="n">
-        <v>150.35</v>
+        <v>149.08</v>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
@@ -729,7 +729,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>2026-09-09T12:34:40+02:00</t>
+          <t>2026-09-09T19:10:37+02:00</t>
         </is>
       </c>
     </row>
@@ -785,13 +785,13 @@
         <v>150</v>
       </c>
       <c r="M3" t="n">
-        <v>152.81</v>
+        <v>152.85</v>
       </c>
       <c r="N3" t="n">
-        <v>152.81</v>
+        <v>152.85</v>
       </c>
       <c r="O3" t="n">
-        <v>2.82</v>
+        <v>2.87</v>
       </c>
       <c r="P3" t="n">
         <v>0.01</v>
@@ -800,10 +800,10 @@
         <v>6</v>
       </c>
       <c r="R3" t="n">
-        <v>-3.19</v>
+        <v>-3.15</v>
       </c>
       <c r="S3" t="n">
-        <v>-2.13</v>
+        <v>-2.1</v>
       </c>
       <c r="T3" t="n">
         <v>0.3</v>
@@ -815,16 +815,16 @@
         <v>18</v>
       </c>
       <c r="W3" t="n">
-        <v>615.54</v>
+        <v>615.59</v>
       </c>
       <c r="X3" t="n">
-        <v>9.539999999999999</v>
+        <v>9.59</v>
       </c>
       <c r="Y3" t="n">
-        <v>2124.38</v>
+        <v>2124.43</v>
       </c>
       <c r="Z3" t="n">
-        <v>168.38</v>
+        <v>168.43</v>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
@@ -868,7 +868,7 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>2026-09-09T12:34:40+02:00</t>
+          <t>2026-09-09T19:10:37+02:00</t>
         </is>
       </c>
     </row>
@@ -924,13 +924,13 @@
         <v>5000</v>
       </c>
       <c r="M4" t="n">
-        <v>4986.59</v>
+        <v>4974.31</v>
       </c>
       <c r="N4" t="n">
-        <v>4986.59</v>
+        <v>4974.31</v>
       </c>
       <c r="O4" t="n">
-        <v>-9.210000000000001</v>
+        <v>-21.5</v>
       </c>
       <c r="P4" t="n">
         <v>4.19</v>
@@ -939,31 +939,31 @@
         <v>6</v>
       </c>
       <c r="R4" t="n">
-        <v>-19.41</v>
+        <v>-31.69</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.39</v>
+        <v>-0.63</v>
       </c>
       <c r="T4" t="n">
         <v>3.4</v>
       </c>
       <c r="U4" t="n">
-        <v>3.08</v>
+        <v>2.84</v>
       </c>
       <c r="V4" t="n">
-        <v>12.91</v>
+        <v>11.86</v>
       </c>
       <c r="W4" t="n">
-        <v>5140.24</v>
+        <v>5115.61</v>
       </c>
       <c r="X4" t="n">
-        <v>134.24</v>
+        <v>109.61</v>
       </c>
       <c r="Y4" t="n">
-        <v>5630.16</v>
+        <v>5564.08</v>
       </c>
       <c r="Z4" t="n">
-        <v>624.16</v>
+        <v>558.08</v>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
@@ -1007,7 +1007,7 @@
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>2026-09-09T12:34:40+02:00</t>
+          <t>2026-09-09T19:10:37+02:00</t>
         </is>
       </c>
     </row>
@@ -1063,13 +1063,13 @@
         <v>5000</v>
       </c>
       <c r="M5" t="n">
-        <v>4983.3</v>
+        <v>4968.71</v>
       </c>
       <c r="N5" t="n">
-        <v>4983.3</v>
+        <v>4968.71</v>
       </c>
       <c r="O5" t="n">
-        <v>-14.99</v>
+        <v>-29.58</v>
       </c>
       <c r="P5" t="n">
         <v>1.71</v>
@@ -1078,35 +1078,35 @@
         <v>6</v>
       </c>
       <c r="R5" t="n">
-        <v>-22.7</v>
+        <v>-37.29</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.45</v>
+        <v>-0.75</v>
       </c>
       <c r="T5" t="n">
         <v>1.39</v>
       </c>
       <c r="U5" t="n">
-        <v>1.91</v>
+        <v>1.62</v>
       </c>
       <c r="V5" t="n">
-        <v>7.85</v>
+        <v>6.62</v>
       </c>
       <c r="W5" t="n">
-        <v>5078.31</v>
+        <v>5048.97</v>
       </c>
       <c r="X5" t="n">
-        <v>72.31</v>
+        <v>42.97</v>
       </c>
       <c r="Y5" t="n">
-        <v>5374.33</v>
+        <v>5297.61</v>
       </c>
       <c r="Z5" t="n">
-        <v>368.33</v>
+        <v>291.61</v>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>Laterale</t>
+          <t>Pressione breve</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -1146,7 +1146,7 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>2026-09-09T12:34:40+02:00</t>
+          <t>2026-09-09T19:10:37+02:00</t>
         </is>
       </c>
     </row>
@@ -1202,13 +1202,13 @@
         <v>5000</v>
       </c>
       <c r="M6" t="n">
-        <v>4983.3</v>
+        <v>4968.71</v>
       </c>
       <c r="N6" t="n">
-        <v>4983.3</v>
+        <v>4968.71</v>
       </c>
       <c r="O6" t="n">
-        <v>-14.99</v>
+        <v>-29.58</v>
       </c>
       <c r="P6" t="n">
         <v>1.71</v>
@@ -1217,35 +1217,35 @@
         <v>6</v>
       </c>
       <c r="R6" t="n">
-        <v>-22.7</v>
+        <v>-37.29</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.45</v>
+        <v>-0.75</v>
       </c>
       <c r="T6" t="n">
         <v>1.39</v>
       </c>
       <c r="U6" t="n">
-        <v>1.91</v>
+        <v>1.62</v>
       </c>
       <c r="V6" t="n">
-        <v>7.85</v>
+        <v>6.62</v>
       </c>
       <c r="W6" t="n">
-        <v>5078.31</v>
+        <v>5048.97</v>
       </c>
       <c r="X6" t="n">
-        <v>72.31</v>
+        <v>42.97</v>
       </c>
       <c r="Y6" t="n">
-        <v>5374.33</v>
+        <v>5297.61</v>
       </c>
       <c r="Z6" t="n">
-        <v>368.33</v>
+        <v>291.61</v>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>Laterale</t>
+          <t>Pressione breve</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -1285,7 +1285,7 @@
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>2026-09-09T12:34:40+02:00</t>
+          <t>2026-09-09T19:10:37+02:00</t>
         </is>
       </c>
     </row>
@@ -1341,13 +1341,13 @@
         <v>5000</v>
       </c>
       <c r="M7" t="n">
-        <v>4983.3</v>
+        <v>4968.71</v>
       </c>
       <c r="N7" t="n">
-        <v>4983.3</v>
+        <v>4968.71</v>
       </c>
       <c r="O7" t="n">
-        <v>-14.99</v>
+        <v>-29.58</v>
       </c>
       <c r="P7" t="n">
         <v>1.71</v>
@@ -1356,35 +1356,35 @@
         <v>6</v>
       </c>
       <c r="R7" t="n">
-        <v>-22.7</v>
+        <v>-37.29</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.45</v>
+        <v>-0.75</v>
       </c>
       <c r="T7" t="n">
         <v>1.39</v>
       </c>
       <c r="U7" t="n">
-        <v>1.91</v>
+        <v>1.62</v>
       </c>
       <c r="V7" t="n">
-        <v>7.85</v>
+        <v>6.62</v>
       </c>
       <c r="W7" t="n">
-        <v>5078.31</v>
+        <v>5048.97</v>
       </c>
       <c r="X7" t="n">
-        <v>72.31</v>
+        <v>42.97</v>
       </c>
       <c r="Y7" t="n">
-        <v>5374.33</v>
+        <v>5297.61</v>
       </c>
       <c r="Z7" t="n">
-        <v>368.33</v>
+        <v>291.61</v>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>Laterale</t>
+          <t>Pressione breve</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -1424,7 +1424,7 @@
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>2026-09-09T12:34:40+02:00</t>
+          <t>2026-09-09T19:10:37+02:00</t>
         </is>
       </c>
     </row>
@@ -1480,13 +1480,13 @@
         <v>5000</v>
       </c>
       <c r="M8" t="n">
-        <v>4937.29</v>
+        <v>4925.75</v>
       </c>
       <c r="N8" t="n">
-        <v>4937.29</v>
+        <v>4925.75</v>
       </c>
       <c r="O8" t="n">
-        <v>-62.34</v>
+        <v>-73.88</v>
       </c>
       <c r="P8" t="n">
         <v>0.37</v>
@@ -1495,31 +1495,31 @@
         <v>6</v>
       </c>
       <c r="R8" t="n">
-        <v>-68.70999999999999</v>
+        <v>-80.25</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.37</v>
+        <v>-1.61</v>
       </c>
       <c r="T8" t="n">
         <v>0.3</v>
       </c>
       <c r="U8" t="n">
-        <v>1.22</v>
+        <v>0.99</v>
       </c>
       <c r="V8" t="n">
-        <v>4.99</v>
+        <v>4.02</v>
       </c>
       <c r="W8" t="n">
-        <v>4997.74</v>
+        <v>4974.49</v>
       </c>
       <c r="X8" t="n">
-        <v>-8.26</v>
+        <v>-31.51</v>
       </c>
       <c r="Y8" t="n">
-        <v>5183.57</v>
+        <v>5123.62</v>
       </c>
       <c r="Z8" t="n">
-        <v>177.57</v>
+        <v>117.62</v>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
@@ -1563,7 +1563,7 @@
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>2026-09-09T12:34:40+02:00</t>
+          <t>2026-09-09T19:10:37+02:00</t>
         </is>
       </c>
     </row>
@@ -1671,7 +1671,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-09T12:34:40+02:00</t>
+          <t>2026-09-09T19:10:37+02:00</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1694,22 +1694,22 @@
         <v>25300</v>
       </c>
       <c r="H2" t="n">
-        <v>25164.12</v>
+        <v>25095.5</v>
       </c>
       <c r="I2" t="n">
-        <v>25164.12</v>
+        <v>25095.5</v>
       </c>
       <c r="J2" t="n">
-        <v>-177.88</v>
+        <v>-246.5</v>
       </c>
       <c r="K2" t="n">
-        <v>-0.7</v>
+        <v>-0.97</v>
       </c>
       <c r="L2" t="n">
-        <v>26588.07</v>
+        <v>26451.1</v>
       </c>
       <c r="M2" t="n">
-        <v>31167.45</v>
+        <v>30810.04</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>

--- a/AlphaForge_Fineco_Decision_Cockpit.xlsx
+++ b/AlphaForge_Fineco_Decision_Cockpit.xlsx
@@ -729,7 +729,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>2026-09-09T19:10:37+02:00</t>
+          <t>2026-09-09T21:16:39+02:00</t>
         </is>
       </c>
     </row>
@@ -868,7 +868,7 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>2026-09-09T19:10:37+02:00</t>
+          <t>2026-09-09T21:16:39+02:00</t>
         </is>
       </c>
     </row>
@@ -1007,7 +1007,7 @@
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>2026-09-09T19:10:37+02:00</t>
+          <t>2026-09-09T21:16:39+02:00</t>
         </is>
       </c>
     </row>
@@ -1146,7 +1146,7 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>2026-09-09T19:10:37+02:00</t>
+          <t>2026-09-09T21:16:39+02:00</t>
         </is>
       </c>
     </row>
@@ -1285,7 +1285,7 @@
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>2026-09-09T19:10:37+02:00</t>
+          <t>2026-09-09T21:16:39+02:00</t>
         </is>
       </c>
     </row>
@@ -1424,7 +1424,7 @@
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>2026-09-09T19:10:37+02:00</t>
+          <t>2026-09-09T21:16:39+02:00</t>
         </is>
       </c>
     </row>
@@ -1563,7 +1563,7 @@
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>2026-09-09T19:10:37+02:00</t>
+          <t>2026-09-09T21:16:39+02:00</t>
         </is>
       </c>
     </row>
@@ -1671,7 +1671,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-09T19:10:37+02:00</t>
+          <t>2026-09-09T21:16:39+02:00</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">

--- a/AlphaForge_Fineco_Decision_Cockpit.xlsx
+++ b/AlphaForge_Fineco_Decision_Cockpit.xlsx
@@ -729,7 +729,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>2026-09-09T21:16:39+02:00</t>
+          <t>2026-09-09T23:44:12+02:00</t>
         </is>
       </c>
     </row>
@@ -868,7 +868,7 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>2026-09-09T21:16:39+02:00</t>
+          <t>2026-09-09T23:44:12+02:00</t>
         </is>
       </c>
     </row>
@@ -1007,7 +1007,7 @@
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>2026-09-09T21:16:39+02:00</t>
+          <t>2026-09-09T23:44:12+02:00</t>
         </is>
       </c>
     </row>
@@ -1146,7 +1146,7 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>2026-09-09T21:16:39+02:00</t>
+          <t>2026-09-09T23:44:12+02:00</t>
         </is>
       </c>
     </row>
@@ -1285,7 +1285,7 @@
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>2026-09-09T21:16:39+02:00</t>
+          <t>2026-09-09T23:44:12+02:00</t>
         </is>
       </c>
     </row>
@@ -1424,7 +1424,7 @@
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>2026-09-09T21:16:39+02:00</t>
+          <t>2026-09-09T23:44:12+02:00</t>
         </is>
       </c>
     </row>
@@ -1563,7 +1563,7 @@
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>2026-09-09T21:16:39+02:00</t>
+          <t>2026-09-09T23:44:12+02:00</t>
         </is>
       </c>
     </row>
@@ -1671,7 +1671,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-09T21:16:39+02:00</t>
+          <t>2026-09-09T23:44:12+02:00</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">

--- a/AlphaForge_Fineco_Decision_Cockpit.xlsx
+++ b/AlphaForge_Fineco_Decision_Cockpit.xlsx
@@ -631,7 +631,7 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
@@ -646,13 +646,13 @@
         <v>150</v>
       </c>
       <c r="M2" t="n">
-        <v>136.46</v>
+        <v>135.69</v>
       </c>
       <c r="N2" t="n">
-        <v>136.46</v>
+        <v>135.69</v>
       </c>
       <c r="O2" t="n">
-        <v>-13.48</v>
+        <v>-14.24</v>
       </c>
       <c r="P2" t="n">
         <v>0.07000000000000001</v>
@@ -661,10 +661,10 @@
         <v>6</v>
       </c>
       <c r="R2" t="n">
-        <v>-19.54</v>
+        <v>-20.31</v>
       </c>
       <c r="S2" t="n">
-        <v>-13.03</v>
+        <v>-13.54</v>
       </c>
       <c r="T2" t="n">
         <v>1.8</v>
@@ -676,16 +676,16 @@
         <v>18</v>
       </c>
       <c r="W2" t="n">
-        <v>598.5</v>
+        <v>597.7</v>
       </c>
       <c r="X2" t="n">
-        <v>-7.5</v>
+        <v>-8.300000000000001</v>
       </c>
       <c r="Y2" t="n">
-        <v>2105.08</v>
+        <v>2104.17</v>
       </c>
       <c r="Z2" t="n">
-        <v>149.08</v>
+        <v>148.17</v>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
@@ -729,7 +729,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>2026-09-09T23:44:12+02:00</t>
+          <t>2026-09-10T14:15:38+02:00</t>
         </is>
       </c>
     </row>
@@ -770,7 +770,7 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
@@ -785,13 +785,13 @@
         <v>150</v>
       </c>
       <c r="M3" t="n">
-        <v>152.85</v>
+        <v>151.54</v>
       </c>
       <c r="N3" t="n">
-        <v>152.85</v>
+        <v>151.54</v>
       </c>
       <c r="O3" t="n">
-        <v>2.87</v>
+        <v>1.55</v>
       </c>
       <c r="P3" t="n">
         <v>0.01</v>
@@ -800,35 +800,35 @@
         <v>6</v>
       </c>
       <c r="R3" t="n">
-        <v>-3.15</v>
+        <v>-4.46</v>
       </c>
       <c r="S3" t="n">
-        <v>-2.1</v>
+        <v>-2.97</v>
       </c>
       <c r="T3" t="n">
         <v>0.3</v>
       </c>
       <c r="U3" t="n">
-        <v>4.22</v>
+        <v>3.87</v>
       </c>
       <c r="V3" t="n">
-        <v>18</v>
+        <v>16.41</v>
       </c>
       <c r="W3" t="n">
-        <v>615.59</v>
+        <v>613.17</v>
       </c>
       <c r="X3" t="n">
-        <v>9.59</v>
+        <v>7.17</v>
       </c>
       <c r="Y3" t="n">
-        <v>2124.43</v>
+        <v>2108.09</v>
       </c>
       <c r="Z3" t="n">
-        <v>168.43</v>
+        <v>152.09</v>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>Rimbalzo breve</t>
+          <t>Laterale</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -868,7 +868,7 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>2026-09-09T23:44:12+02:00</t>
+          <t>2026-09-10T14:15:38+02:00</t>
         </is>
       </c>
     </row>
@@ -909,7 +909,7 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I4" t="n">
         <v>5000</v>
@@ -924,22 +924,22 @@
         <v>5000</v>
       </c>
       <c r="M4" t="n">
-        <v>4974.31</v>
+        <v>4974.46</v>
       </c>
       <c r="N4" t="n">
-        <v>4974.31</v>
+        <v>4974.46</v>
       </c>
       <c r="O4" t="n">
-        <v>-21.5</v>
+        <v>-20.89</v>
       </c>
       <c r="P4" t="n">
-        <v>4.19</v>
+        <v>4.66</v>
       </c>
       <c r="Q4" t="n">
         <v>6</v>
       </c>
       <c r="R4" t="n">
-        <v>-31.69</v>
+        <v>-31.54</v>
       </c>
       <c r="S4" t="n">
         <v>-0.63</v>
@@ -948,22 +948,22 @@
         <v>3.4</v>
       </c>
       <c r="U4" t="n">
-        <v>2.84</v>
+        <v>2.69</v>
       </c>
       <c r="V4" t="n">
-        <v>11.86</v>
+        <v>11.19</v>
       </c>
       <c r="W4" t="n">
-        <v>5115.61</v>
+        <v>5108.08</v>
       </c>
       <c r="X4" t="n">
-        <v>109.61</v>
+        <v>102.08</v>
       </c>
       <c r="Y4" t="n">
-        <v>5564.08</v>
+        <v>5530.87</v>
       </c>
       <c r="Z4" t="n">
-        <v>558.08</v>
+        <v>524.87</v>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
@@ -1007,7 +1007,7 @@
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>2026-09-09T23:44:12+02:00</t>
+          <t>2026-09-10T14:15:38+02:00</t>
         </is>
       </c>
     </row>
@@ -1048,7 +1048,7 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I5" t="n">
         <v>5000</v>
@@ -1063,46 +1063,46 @@
         <v>5000</v>
       </c>
       <c r="M5" t="n">
-        <v>4968.71</v>
+        <v>4964.97</v>
       </c>
       <c r="N5" t="n">
-        <v>4968.71</v>
+        <v>4964.97</v>
       </c>
       <c r="O5" t="n">
-        <v>-29.58</v>
+        <v>-33.13</v>
       </c>
       <c r="P5" t="n">
-        <v>1.71</v>
+        <v>1.9</v>
       </c>
       <c r="Q5" t="n">
         <v>6</v>
       </c>
       <c r="R5" t="n">
-        <v>-37.29</v>
+        <v>-41.03</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.75</v>
+        <v>-0.82</v>
       </c>
       <c r="T5" t="n">
         <v>1.39</v>
       </c>
       <c r="U5" t="n">
-        <v>1.62</v>
+        <v>1.09</v>
       </c>
       <c r="V5" t="n">
-        <v>6.62</v>
+        <v>4.43</v>
       </c>
       <c r="W5" t="n">
-        <v>5048.97</v>
+        <v>5019.03</v>
       </c>
       <c r="X5" t="n">
-        <v>42.97</v>
+        <v>13.03</v>
       </c>
       <c r="Y5" t="n">
-        <v>5297.61</v>
+        <v>5184.76</v>
       </c>
       <c r="Z5" t="n">
-        <v>291.61</v>
+        <v>178.76</v>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
@@ -1146,7 +1146,7 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>2026-09-09T23:44:12+02:00</t>
+          <t>2026-09-10T14:15:38+02:00</t>
         </is>
       </c>
     </row>
@@ -1187,7 +1187,7 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I6" t="n">
         <v>5000</v>
@@ -1202,46 +1202,46 @@
         <v>5000</v>
       </c>
       <c r="M6" t="n">
-        <v>4968.71</v>
+        <v>4964.97</v>
       </c>
       <c r="N6" t="n">
-        <v>4968.71</v>
+        <v>4964.97</v>
       </c>
       <c r="O6" t="n">
-        <v>-29.58</v>
+        <v>-33.13</v>
       </c>
       <c r="P6" t="n">
-        <v>1.71</v>
+        <v>1.9</v>
       </c>
       <c r="Q6" t="n">
         <v>6</v>
       </c>
       <c r="R6" t="n">
-        <v>-37.29</v>
+        <v>-41.03</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.75</v>
+        <v>-0.82</v>
       </c>
       <c r="T6" t="n">
         <v>1.39</v>
       </c>
       <c r="U6" t="n">
-        <v>1.62</v>
+        <v>1.09</v>
       </c>
       <c r="V6" t="n">
-        <v>6.62</v>
+        <v>4.43</v>
       </c>
       <c r="W6" t="n">
-        <v>5048.97</v>
+        <v>5019.03</v>
       </c>
       <c r="X6" t="n">
-        <v>42.97</v>
+        <v>13.03</v>
       </c>
       <c r="Y6" t="n">
-        <v>5297.61</v>
+        <v>5184.76</v>
       </c>
       <c r="Z6" t="n">
-        <v>291.61</v>
+        <v>178.76</v>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
@@ -1285,7 +1285,7 @@
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>2026-09-09T23:44:12+02:00</t>
+          <t>2026-09-10T14:15:38+02:00</t>
         </is>
       </c>
     </row>
@@ -1326,7 +1326,7 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I7" t="n">
         <v>5000</v>
@@ -1341,46 +1341,46 @@
         <v>5000</v>
       </c>
       <c r="M7" t="n">
-        <v>4968.71</v>
+        <v>4964.97</v>
       </c>
       <c r="N7" t="n">
-        <v>4968.71</v>
+        <v>4964.97</v>
       </c>
       <c r="O7" t="n">
-        <v>-29.58</v>
+        <v>-33.13</v>
       </c>
       <c r="P7" t="n">
-        <v>1.71</v>
+        <v>1.9</v>
       </c>
       <c r="Q7" t="n">
         <v>6</v>
       </c>
       <c r="R7" t="n">
-        <v>-37.29</v>
+        <v>-41.03</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.75</v>
+        <v>-0.82</v>
       </c>
       <c r="T7" t="n">
         <v>1.39</v>
       </c>
       <c r="U7" t="n">
-        <v>1.62</v>
+        <v>1.09</v>
       </c>
       <c r="V7" t="n">
-        <v>6.62</v>
+        <v>4.43</v>
       </c>
       <c r="W7" t="n">
-        <v>5048.97</v>
+        <v>5019.03</v>
       </c>
       <c r="X7" t="n">
-        <v>42.97</v>
+        <v>13.03</v>
       </c>
       <c r="Y7" t="n">
-        <v>5297.61</v>
+        <v>5184.76</v>
       </c>
       <c r="Z7" t="n">
-        <v>291.61</v>
+        <v>178.76</v>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
@@ -1424,7 +1424,7 @@
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>2026-09-09T23:44:12+02:00</t>
+          <t>2026-09-10T14:15:38+02:00</t>
         </is>
       </c>
     </row>
@@ -1465,7 +1465,7 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I8" t="n">
         <v>5000</v>
@@ -1480,46 +1480,46 @@
         <v>5000</v>
       </c>
       <c r="M8" t="n">
-        <v>4925.75</v>
+        <v>4908.01</v>
       </c>
       <c r="N8" t="n">
-        <v>4925.75</v>
+        <v>4908.01</v>
       </c>
       <c r="O8" t="n">
-        <v>-73.88</v>
+        <v>-91.58</v>
       </c>
       <c r="P8" t="n">
-        <v>0.37</v>
+        <v>0.41</v>
       </c>
       <c r="Q8" t="n">
         <v>6</v>
       </c>
       <c r="R8" t="n">
-        <v>-80.25</v>
+        <v>-97.98999999999999</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.61</v>
+        <v>-1.96</v>
       </c>
       <c r="T8" t="n">
         <v>0.3</v>
       </c>
       <c r="U8" t="n">
-        <v>0.99</v>
+        <v>0.64</v>
       </c>
       <c r="V8" t="n">
-        <v>4.02</v>
+        <v>2.59</v>
       </c>
       <c r="W8" t="n">
-        <v>4974.49</v>
+        <v>4939.47</v>
       </c>
       <c r="X8" t="n">
-        <v>-31.51</v>
+        <v>-66.53</v>
       </c>
       <c r="Y8" t="n">
-        <v>5123.62</v>
+        <v>5035.08</v>
       </c>
       <c r="Z8" t="n">
-        <v>117.62</v>
+        <v>29.08</v>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
@@ -1563,7 +1563,7 @@
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>2026-09-09T23:44:12+02:00</t>
+          <t>2026-09-10T14:15:38+02:00</t>
         </is>
       </c>
     </row>
@@ -1671,17 +1671,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-09T23:44:12+02:00</t>
+          <t>2026-09-10T14:15:38+02:00</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -1694,22 +1694,22 @@
         <v>25300</v>
       </c>
       <c r="H2" t="n">
-        <v>25095.5</v>
+        <v>25064.61</v>
       </c>
       <c r="I2" t="n">
-        <v>25095.5</v>
+        <v>25064.61</v>
       </c>
       <c r="J2" t="n">
-        <v>-246.5</v>
+        <v>-277.39</v>
       </c>
       <c r="K2" t="n">
-        <v>-0.97</v>
+        <v>-1.1</v>
       </c>
       <c r="L2" t="n">
-        <v>26451.1</v>
+        <v>26315.51</v>
       </c>
       <c r="M2" t="n">
-        <v>30810.04</v>
+        <v>30332.49</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>

--- a/AlphaForge_Fineco_Decision_Cockpit.xlsx
+++ b/AlphaForge_Fineco_Decision_Cockpit.xlsx
@@ -646,13 +646,13 @@
         <v>150</v>
       </c>
       <c r="M2" t="n">
-        <v>135.69</v>
+        <v>136.3</v>
       </c>
       <c r="N2" t="n">
-        <v>135.69</v>
+        <v>136.3</v>
       </c>
       <c r="O2" t="n">
-        <v>-14.24</v>
+        <v>-13.62</v>
       </c>
       <c r="P2" t="n">
         <v>0.07000000000000001</v>
@@ -661,10 +661,10 @@
         <v>6</v>
       </c>
       <c r="R2" t="n">
-        <v>-20.31</v>
+        <v>-19.7</v>
       </c>
       <c r="S2" t="n">
-        <v>-13.54</v>
+        <v>-13.13</v>
       </c>
       <c r="T2" t="n">
         <v>1.8</v>
@@ -676,20 +676,20 @@
         <v>18</v>
       </c>
       <c r="W2" t="n">
-        <v>597.7</v>
+        <v>598.34</v>
       </c>
       <c r="X2" t="n">
-        <v>-8.300000000000001</v>
+        <v>-7.66</v>
       </c>
       <c r="Y2" t="n">
-        <v>2104.17</v>
+        <v>2104.9</v>
       </c>
       <c r="Z2" t="n">
-        <v>148.17</v>
+        <v>148.9</v>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>Pressione breve</t>
+          <t>Laterale</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -729,7 +729,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>2026-09-10T14:15:38+02:00</t>
+          <t>2026-09-10T16:30:28+02:00</t>
         </is>
       </c>
     </row>
@@ -785,13 +785,13 @@
         <v>150</v>
       </c>
       <c r="M3" t="n">
-        <v>151.54</v>
+        <v>149.92</v>
       </c>
       <c r="N3" t="n">
-        <v>151.54</v>
+        <v>149.92</v>
       </c>
       <c r="O3" t="n">
-        <v>1.55</v>
+        <v>-0.06</v>
       </c>
       <c r="P3" t="n">
         <v>0.01</v>
@@ -800,31 +800,31 @@
         <v>6</v>
       </c>
       <c r="R3" t="n">
-        <v>-4.46</v>
+        <v>-6.08</v>
       </c>
       <c r="S3" t="n">
-        <v>-2.97</v>
+        <v>-4.05</v>
       </c>
       <c r="T3" t="n">
         <v>0.3</v>
       </c>
       <c r="U3" t="n">
-        <v>3.87</v>
+        <v>2.84</v>
       </c>
       <c r="V3" t="n">
-        <v>16.41</v>
+        <v>11.87</v>
       </c>
       <c r="W3" t="n">
-        <v>613.17</v>
+        <v>608.42</v>
       </c>
       <c r="X3" t="n">
-        <v>7.17</v>
+        <v>2.42</v>
       </c>
       <c r="Y3" t="n">
-        <v>2108.09</v>
+        <v>2063.62</v>
       </c>
       <c r="Z3" t="n">
-        <v>152.09</v>
+        <v>107.62</v>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
@@ -868,7 +868,7 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>2026-09-10T14:15:38+02:00</t>
+          <t>2026-09-10T16:30:28+02:00</t>
         </is>
       </c>
     </row>
@@ -924,13 +924,13 @@
         <v>5000</v>
       </c>
       <c r="M4" t="n">
-        <v>4974.46</v>
+        <v>4951.11</v>
       </c>
       <c r="N4" t="n">
-        <v>4974.46</v>
+        <v>4951.11</v>
       </c>
       <c r="O4" t="n">
-        <v>-20.89</v>
+        <v>-44.23</v>
       </c>
       <c r="P4" t="n">
         <v>4.66</v>
@@ -939,31 +939,31 @@
         <v>6</v>
       </c>
       <c r="R4" t="n">
-        <v>-31.54</v>
+        <v>-54.89</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.63</v>
+        <v>-1.1</v>
       </c>
       <c r="T4" t="n">
         <v>3.4</v>
       </c>
       <c r="U4" t="n">
-        <v>2.69</v>
+        <v>2.22</v>
       </c>
       <c r="V4" t="n">
-        <v>11.19</v>
+        <v>9.19</v>
       </c>
       <c r="W4" t="n">
-        <v>5108.08</v>
+        <v>5061.19</v>
       </c>
       <c r="X4" t="n">
-        <v>102.08</v>
+        <v>55.19</v>
       </c>
       <c r="Y4" t="n">
-        <v>5530.87</v>
+        <v>5406.35</v>
       </c>
       <c r="Z4" t="n">
-        <v>524.87</v>
+        <v>400.35</v>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
@@ -1007,7 +1007,7 @@
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>2026-09-10T14:15:38+02:00</t>
+          <t>2026-09-10T16:30:28+02:00</t>
         </is>
       </c>
     </row>
@@ -1063,13 +1063,13 @@
         <v>5000</v>
       </c>
       <c r="M5" t="n">
-        <v>4964.97</v>
+        <v>4937.76</v>
       </c>
       <c r="N5" t="n">
-        <v>4964.97</v>
+        <v>4937.76</v>
       </c>
       <c r="O5" t="n">
-        <v>-33.13</v>
+        <v>-60.34</v>
       </c>
       <c r="P5" t="n">
         <v>1.9</v>
@@ -1078,31 +1078,31 @@
         <v>6</v>
       </c>
       <c r="R5" t="n">
-        <v>-41.03</v>
+        <v>-68.23999999999999</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.82</v>
+        <v>-1.36</v>
       </c>
       <c r="T5" t="n">
         <v>1.39</v>
       </c>
       <c r="U5" t="n">
-        <v>1.09</v>
+        <v>0.53</v>
       </c>
       <c r="V5" t="n">
-        <v>4.43</v>
+        <v>2.15</v>
       </c>
       <c r="W5" t="n">
-        <v>5019.03</v>
+        <v>4964.07</v>
       </c>
       <c r="X5" t="n">
-        <v>13.03</v>
+        <v>-41.93</v>
       </c>
       <c r="Y5" t="n">
-        <v>5184.76</v>
+        <v>5043.85</v>
       </c>
       <c r="Z5" t="n">
-        <v>178.76</v>
+        <v>37.85</v>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
@@ -1146,7 +1146,7 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>2026-09-10T14:15:38+02:00</t>
+          <t>2026-09-10T16:30:28+02:00</t>
         </is>
       </c>
     </row>
@@ -1202,13 +1202,13 @@
         <v>5000</v>
       </c>
       <c r="M6" t="n">
-        <v>4964.97</v>
+        <v>4937.76</v>
       </c>
       <c r="N6" t="n">
-        <v>4964.97</v>
+        <v>4937.76</v>
       </c>
       <c r="O6" t="n">
-        <v>-33.13</v>
+        <v>-60.34</v>
       </c>
       <c r="P6" t="n">
         <v>1.9</v>
@@ -1217,31 +1217,31 @@
         <v>6</v>
       </c>
       <c r="R6" t="n">
-        <v>-41.03</v>
+        <v>-68.23999999999999</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.82</v>
+        <v>-1.36</v>
       </c>
       <c r="T6" t="n">
         <v>1.39</v>
       </c>
       <c r="U6" t="n">
-        <v>1.09</v>
+        <v>0.53</v>
       </c>
       <c r="V6" t="n">
-        <v>4.43</v>
+        <v>2.15</v>
       </c>
       <c r="W6" t="n">
-        <v>5019.03</v>
+        <v>4964.07</v>
       </c>
       <c r="X6" t="n">
-        <v>13.03</v>
+        <v>-41.93</v>
       </c>
       <c r="Y6" t="n">
-        <v>5184.76</v>
+        <v>5043.85</v>
       </c>
       <c r="Z6" t="n">
-        <v>178.76</v>
+        <v>37.85</v>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
@@ -1285,7 +1285,7 @@
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>2026-09-10T14:15:38+02:00</t>
+          <t>2026-09-10T16:30:28+02:00</t>
         </is>
       </c>
     </row>
@@ -1341,13 +1341,13 @@
         <v>5000</v>
       </c>
       <c r="M7" t="n">
-        <v>4964.97</v>
+        <v>4937.76</v>
       </c>
       <c r="N7" t="n">
-        <v>4964.97</v>
+        <v>4937.76</v>
       </c>
       <c r="O7" t="n">
-        <v>-33.13</v>
+        <v>-60.34</v>
       </c>
       <c r="P7" t="n">
         <v>1.9</v>
@@ -1356,31 +1356,31 @@
         <v>6</v>
       </c>
       <c r="R7" t="n">
-        <v>-41.03</v>
+        <v>-68.23999999999999</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.82</v>
+        <v>-1.36</v>
       </c>
       <c r="T7" t="n">
         <v>1.39</v>
       </c>
       <c r="U7" t="n">
-        <v>1.09</v>
+        <v>0.53</v>
       </c>
       <c r="V7" t="n">
-        <v>4.43</v>
+        <v>2.15</v>
       </c>
       <c r="W7" t="n">
-        <v>5019.03</v>
+        <v>4964.07</v>
       </c>
       <c r="X7" t="n">
-        <v>13.03</v>
+        <v>-41.93</v>
       </c>
       <c r="Y7" t="n">
-        <v>5184.76</v>
+        <v>5043.85</v>
       </c>
       <c r="Z7" t="n">
-        <v>178.76</v>
+        <v>37.85</v>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
@@ -1424,7 +1424,7 @@
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>2026-09-10T14:15:38+02:00</t>
+          <t>2026-09-10T16:30:28+02:00</t>
         </is>
       </c>
     </row>
@@ -1480,13 +1480,13 @@
         <v>5000</v>
       </c>
       <c r="M8" t="n">
-        <v>4908.01</v>
+        <v>4886.46</v>
       </c>
       <c r="N8" t="n">
-        <v>4908.01</v>
+        <v>4886.46</v>
       </c>
       <c r="O8" t="n">
-        <v>-91.58</v>
+        <v>-113.13</v>
       </c>
       <c r="P8" t="n">
         <v>0.41</v>
@@ -1495,31 +1495,31 @@
         <v>6</v>
       </c>
       <c r="R8" t="n">
-        <v>-97.98999999999999</v>
+        <v>-119.54</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.96</v>
+        <v>-2.39</v>
       </c>
       <c r="T8" t="n">
         <v>0.3</v>
       </c>
       <c r="U8" t="n">
-        <v>0.64</v>
+        <v>0.19</v>
       </c>
       <c r="V8" t="n">
-        <v>2.59</v>
+        <v>0.78</v>
       </c>
       <c r="W8" t="n">
-        <v>4939.47</v>
+        <v>4895.92</v>
       </c>
       <c r="X8" t="n">
-        <v>-66.53</v>
+        <v>-110.08</v>
       </c>
       <c r="Y8" t="n">
-        <v>5035.08</v>
+        <v>4924.4</v>
       </c>
       <c r="Z8" t="n">
-        <v>29.08</v>
+        <v>-81.59999999999999</v>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
@@ -1563,7 +1563,7 @@
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>2026-09-10T14:15:38+02:00</t>
+          <t>2026-09-10T16:30:28+02:00</t>
         </is>
       </c>
     </row>
@@ -1671,7 +1671,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-10T14:15:38+02:00</t>
+          <t>2026-09-10T16:30:28+02:00</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1694,22 +1694,22 @@
         <v>25300</v>
       </c>
       <c r="H2" t="n">
-        <v>25064.61</v>
+        <v>24937.07</v>
       </c>
       <c r="I2" t="n">
-        <v>25064.61</v>
+        <v>24937.07</v>
       </c>
       <c r="J2" t="n">
-        <v>-277.39</v>
+        <v>-404.93</v>
       </c>
       <c r="K2" t="n">
-        <v>-1.1</v>
+        <v>-1.6</v>
       </c>
       <c r="L2" t="n">
-        <v>26315.51</v>
+        <v>26056.08</v>
       </c>
       <c r="M2" t="n">
-        <v>30332.49</v>
+        <v>29630.82</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>

--- a/AlphaForge_Fineco_Decision_Cockpit.xlsx
+++ b/AlphaForge_Fineco_Decision_Cockpit.xlsx
@@ -646,13 +646,13 @@
         <v>150</v>
       </c>
       <c r="M2" t="n">
-        <v>136.3</v>
+        <v>136.65</v>
       </c>
       <c r="N2" t="n">
-        <v>136.3</v>
+        <v>136.65</v>
       </c>
       <c r="O2" t="n">
-        <v>-13.62</v>
+        <v>-13.27</v>
       </c>
       <c r="P2" t="n">
         <v>0.07000000000000001</v>
@@ -661,10 +661,10 @@
         <v>6</v>
       </c>
       <c r="R2" t="n">
-        <v>-19.7</v>
+        <v>-19.35</v>
       </c>
       <c r="S2" t="n">
-        <v>-13.13</v>
+        <v>-12.9</v>
       </c>
       <c r="T2" t="n">
         <v>1.8</v>
@@ -676,16 +676,16 @@
         <v>18</v>
       </c>
       <c r="W2" t="n">
-        <v>598.34</v>
+        <v>598.71</v>
       </c>
       <c r="X2" t="n">
-        <v>-7.66</v>
+        <v>-7.29</v>
       </c>
       <c r="Y2" t="n">
-        <v>2104.9</v>
+        <v>2105.32</v>
       </c>
       <c r="Z2" t="n">
-        <v>148.9</v>
+        <v>149.32</v>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
@@ -729,7 +729,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>2026-09-10T16:30:28+02:00</t>
+          <t>2026-09-10T19:00:21+02:00</t>
         </is>
       </c>
     </row>
@@ -785,13 +785,13 @@
         <v>150</v>
       </c>
       <c r="M3" t="n">
-        <v>149.92</v>
+        <v>150.43</v>
       </c>
       <c r="N3" t="n">
-        <v>149.92</v>
+        <v>150.43</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.06</v>
+        <v>0.44</v>
       </c>
       <c r="P3" t="n">
         <v>0.01</v>
@@ -800,31 +800,31 @@
         <v>6</v>
       </c>
       <c r="R3" t="n">
-        <v>-6.08</v>
+        <v>-5.57</v>
       </c>
       <c r="S3" t="n">
-        <v>-4.05</v>
+        <v>-3.71</v>
       </c>
       <c r="T3" t="n">
         <v>0.3</v>
       </c>
       <c r="U3" t="n">
-        <v>2.84</v>
+        <v>3.17</v>
       </c>
       <c r="V3" t="n">
-        <v>11.87</v>
+        <v>13.29</v>
       </c>
       <c r="W3" t="n">
-        <v>608.42</v>
+        <v>609.92</v>
       </c>
       <c r="X3" t="n">
-        <v>2.42</v>
+        <v>3.92</v>
       </c>
       <c r="Y3" t="n">
-        <v>2063.62</v>
+        <v>2077.61</v>
       </c>
       <c r="Z3" t="n">
-        <v>107.62</v>
+        <v>121.61</v>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
@@ -868,7 +868,7 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>2026-09-10T16:30:28+02:00</t>
+          <t>2026-09-10T19:00:21+02:00</t>
         </is>
       </c>
     </row>
@@ -924,13 +924,13 @@
         <v>5000</v>
       </c>
       <c r="M4" t="n">
-        <v>4951.11</v>
+        <v>4949.27</v>
       </c>
       <c r="N4" t="n">
-        <v>4951.11</v>
+        <v>4949.27</v>
       </c>
       <c r="O4" t="n">
-        <v>-44.23</v>
+        <v>-46.07</v>
       </c>
       <c r="P4" t="n">
         <v>4.66</v>
@@ -939,31 +939,31 @@
         <v>6</v>
       </c>
       <c r="R4" t="n">
-        <v>-54.89</v>
+        <v>-56.73</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.1</v>
+        <v>-1.13</v>
       </c>
       <c r="T4" t="n">
         <v>3.4</v>
       </c>
       <c r="U4" t="n">
-        <v>2.22</v>
+        <v>2.19</v>
       </c>
       <c r="V4" t="n">
-        <v>9.19</v>
+        <v>9.039999999999999</v>
       </c>
       <c r="W4" t="n">
-        <v>5061.19</v>
+        <v>5057.49</v>
       </c>
       <c r="X4" t="n">
-        <v>55.19</v>
+        <v>51.49</v>
       </c>
       <c r="Y4" t="n">
-        <v>5406.35</v>
+        <v>5396.56</v>
       </c>
       <c r="Z4" t="n">
-        <v>400.35</v>
+        <v>390.56</v>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
@@ -1007,7 +1007,7 @@
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>2026-09-10T16:30:28+02:00</t>
+          <t>2026-09-10T19:00:21+02:00</t>
         </is>
       </c>
     </row>
@@ -1063,13 +1063,13 @@
         <v>5000</v>
       </c>
       <c r="M5" t="n">
-        <v>4937.76</v>
+        <v>4944.46</v>
       </c>
       <c r="N5" t="n">
-        <v>4937.76</v>
+        <v>4944.46</v>
       </c>
       <c r="O5" t="n">
-        <v>-60.34</v>
+        <v>-53.64</v>
       </c>
       <c r="P5" t="n">
         <v>1.9</v>
@@ -1078,31 +1078,31 @@
         <v>6</v>
       </c>
       <c r="R5" t="n">
-        <v>-68.23999999999999</v>
+        <v>-61.54</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.36</v>
+        <v>-1.23</v>
       </c>
       <c r="T5" t="n">
         <v>1.39</v>
       </c>
       <c r="U5" t="n">
-        <v>0.53</v>
+        <v>0.67</v>
       </c>
       <c r="V5" t="n">
-        <v>2.15</v>
+        <v>2.71</v>
       </c>
       <c r="W5" t="n">
-        <v>4964.07</v>
+        <v>4977.62</v>
       </c>
       <c r="X5" t="n">
-        <v>-41.93</v>
+        <v>-28.38</v>
       </c>
       <c r="Y5" t="n">
-        <v>5043.85</v>
+        <v>5078.45</v>
       </c>
       <c r="Z5" t="n">
-        <v>37.85</v>
+        <v>72.45</v>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
@@ -1146,7 +1146,7 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>2026-09-10T16:30:28+02:00</t>
+          <t>2026-09-10T19:00:21+02:00</t>
         </is>
       </c>
     </row>
@@ -1202,13 +1202,13 @@
         <v>5000</v>
       </c>
       <c r="M6" t="n">
-        <v>4937.76</v>
+        <v>4944.46</v>
       </c>
       <c r="N6" t="n">
-        <v>4937.76</v>
+        <v>4944.46</v>
       </c>
       <c r="O6" t="n">
-        <v>-60.34</v>
+        <v>-53.64</v>
       </c>
       <c r="P6" t="n">
         <v>1.9</v>
@@ -1217,31 +1217,31 @@
         <v>6</v>
       </c>
       <c r="R6" t="n">
-        <v>-68.23999999999999</v>
+        <v>-61.54</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.36</v>
+        <v>-1.23</v>
       </c>
       <c r="T6" t="n">
         <v>1.39</v>
       </c>
       <c r="U6" t="n">
-        <v>0.53</v>
+        <v>0.67</v>
       </c>
       <c r="V6" t="n">
-        <v>2.15</v>
+        <v>2.71</v>
       </c>
       <c r="W6" t="n">
-        <v>4964.07</v>
+        <v>4977.62</v>
       </c>
       <c r="X6" t="n">
-        <v>-41.93</v>
+        <v>-28.38</v>
       </c>
       <c r="Y6" t="n">
-        <v>5043.85</v>
+        <v>5078.45</v>
       </c>
       <c r="Z6" t="n">
-        <v>37.85</v>
+        <v>72.45</v>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
@@ -1285,7 +1285,7 @@
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>2026-09-10T16:30:28+02:00</t>
+          <t>2026-09-10T19:00:21+02:00</t>
         </is>
       </c>
     </row>
@@ -1341,13 +1341,13 @@
         <v>5000</v>
       </c>
       <c r="M7" t="n">
-        <v>4937.76</v>
+        <v>4944.46</v>
       </c>
       <c r="N7" t="n">
-        <v>4937.76</v>
+        <v>4944.46</v>
       </c>
       <c r="O7" t="n">
-        <v>-60.34</v>
+        <v>-53.64</v>
       </c>
       <c r="P7" t="n">
         <v>1.9</v>
@@ -1356,31 +1356,31 @@
         <v>6</v>
       </c>
       <c r="R7" t="n">
-        <v>-68.23999999999999</v>
+        <v>-61.54</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.36</v>
+        <v>-1.23</v>
       </c>
       <c r="T7" t="n">
         <v>1.39</v>
       </c>
       <c r="U7" t="n">
-        <v>0.53</v>
+        <v>0.67</v>
       </c>
       <c r="V7" t="n">
-        <v>2.15</v>
+        <v>2.71</v>
       </c>
       <c r="W7" t="n">
-        <v>4964.07</v>
+        <v>4977.62</v>
       </c>
       <c r="X7" t="n">
-        <v>-41.93</v>
+        <v>-28.38</v>
       </c>
       <c r="Y7" t="n">
-        <v>5043.85</v>
+        <v>5078.45</v>
       </c>
       <c r="Z7" t="n">
-        <v>37.85</v>
+        <v>72.45</v>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
@@ -1424,7 +1424,7 @@
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>2026-09-10T16:30:28+02:00</t>
+          <t>2026-09-10T19:00:21+02:00</t>
         </is>
       </c>
     </row>
@@ -1480,13 +1480,13 @@
         <v>5000</v>
       </c>
       <c r="M8" t="n">
-        <v>4886.46</v>
+        <v>4885.69</v>
       </c>
       <c r="N8" t="n">
-        <v>4886.46</v>
+        <v>4885.69</v>
       </c>
       <c r="O8" t="n">
-        <v>-113.13</v>
+        <v>-113.9</v>
       </c>
       <c r="P8" t="n">
         <v>0.41</v>
@@ -1495,31 +1495,31 @@
         <v>6</v>
       </c>
       <c r="R8" t="n">
-        <v>-119.54</v>
+        <v>-120.31</v>
       </c>
       <c r="S8" t="n">
-        <v>-2.39</v>
+        <v>-2.41</v>
       </c>
       <c r="T8" t="n">
         <v>0.3</v>
       </c>
       <c r="U8" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="V8" t="n">
-        <v>0.78</v>
+        <v>0.71</v>
       </c>
       <c r="W8" t="n">
-        <v>4895.92</v>
+        <v>4894.36</v>
       </c>
       <c r="X8" t="n">
-        <v>-110.08</v>
+        <v>-111.64</v>
       </c>
       <c r="Y8" t="n">
-        <v>4924.4</v>
+        <v>4920.46</v>
       </c>
       <c r="Z8" t="n">
-        <v>-81.59999999999999</v>
+        <v>-85.54000000000001</v>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
@@ -1563,7 +1563,7 @@
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>2026-09-10T16:30:28+02:00</t>
+          <t>2026-09-10T19:00:21+02:00</t>
         </is>
       </c>
     </row>
@@ -1671,7 +1671,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-10T16:30:28+02:00</t>
+          <t>2026-09-10T19:00:21+02:00</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1694,22 +1694,22 @@
         <v>25300</v>
       </c>
       <c r="H2" t="n">
-        <v>24937.07</v>
+        <v>24955.42</v>
       </c>
       <c r="I2" t="n">
-        <v>24937.07</v>
+        <v>24955.42</v>
       </c>
       <c r="J2" t="n">
-        <v>-404.93</v>
+        <v>-386.58</v>
       </c>
       <c r="K2" t="n">
-        <v>-1.6</v>
+        <v>-1.53</v>
       </c>
       <c r="L2" t="n">
-        <v>26056.08</v>
+        <v>26093.34</v>
       </c>
       <c r="M2" t="n">
-        <v>29630.82</v>
+        <v>29735.3</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>

--- a/AlphaForge_Fineco_Decision_Cockpit.xlsx
+++ b/AlphaForge_Fineco_Decision_Cockpit.xlsx
@@ -729,7 +729,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>2026-09-10T19:00:21+02:00</t>
+          <t>2026-09-10T21:07:54+02:00</t>
         </is>
       </c>
     </row>
@@ -868,7 +868,7 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>2026-09-10T19:00:21+02:00</t>
+          <t>2026-09-10T21:07:54+02:00</t>
         </is>
       </c>
     </row>
@@ -1007,7 +1007,7 @@
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>2026-09-10T19:00:21+02:00</t>
+          <t>2026-09-10T21:07:54+02:00</t>
         </is>
       </c>
     </row>
@@ -1146,7 +1146,7 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>2026-09-10T19:00:21+02:00</t>
+          <t>2026-09-10T21:07:54+02:00</t>
         </is>
       </c>
     </row>
@@ -1285,7 +1285,7 @@
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>2026-09-10T19:00:21+02:00</t>
+          <t>2026-09-10T21:07:54+02:00</t>
         </is>
       </c>
     </row>
@@ -1424,7 +1424,7 @@
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>2026-09-10T19:00:21+02:00</t>
+          <t>2026-09-10T21:07:54+02:00</t>
         </is>
       </c>
     </row>
@@ -1563,7 +1563,7 @@
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>2026-09-10T19:00:21+02:00</t>
+          <t>2026-09-10T21:07:54+02:00</t>
         </is>
       </c>
     </row>
@@ -1671,7 +1671,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-10T19:00:21+02:00</t>
+          <t>2026-09-10T21:07:54+02:00</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">

--- a/AlphaForge_Fineco_Decision_Cockpit.xlsx
+++ b/AlphaForge_Fineco_Decision_Cockpit.xlsx
@@ -729,7 +729,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>2026-09-10T21:07:54+02:00</t>
+          <t>2026-09-10T23:40:25+02:00</t>
         </is>
       </c>
     </row>
@@ -868,7 +868,7 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>2026-09-10T21:07:54+02:00</t>
+          <t>2026-09-10T23:40:25+02:00</t>
         </is>
       </c>
     </row>
@@ -1007,7 +1007,7 @@
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>2026-09-10T21:07:54+02:00</t>
+          <t>2026-09-10T23:40:25+02:00</t>
         </is>
       </c>
     </row>
@@ -1146,7 +1146,7 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>2026-09-10T21:07:54+02:00</t>
+          <t>2026-09-10T23:40:25+02:00</t>
         </is>
       </c>
     </row>
@@ -1285,7 +1285,7 @@
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>2026-09-10T21:07:54+02:00</t>
+          <t>2026-09-10T23:40:25+02:00</t>
         </is>
       </c>
     </row>
@@ -1424,7 +1424,7 @@
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>2026-09-10T21:07:54+02:00</t>
+          <t>2026-09-10T23:40:25+02:00</t>
         </is>
       </c>
     </row>
@@ -1563,7 +1563,7 @@
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>2026-09-10T21:07:54+02:00</t>
+          <t>2026-09-10T23:40:25+02:00</t>
         </is>
       </c>
     </row>
@@ -1671,7 +1671,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-10T21:07:54+02:00</t>
+          <t>2026-09-10T23:40:25+02:00</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">

--- a/AlphaForge_Fineco_Decision_Cockpit.xlsx
+++ b/AlphaForge_Fineco_Decision_Cockpit.xlsx
@@ -631,7 +631,7 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
@@ -646,25 +646,25 @@
         <v>150</v>
       </c>
       <c r="M2" t="n">
-        <v>136.65</v>
+        <v>136.28</v>
       </c>
       <c r="N2" t="n">
-        <v>136.65</v>
+        <v>136.28</v>
       </c>
       <c r="O2" t="n">
-        <v>-13.27</v>
+        <v>-13.64</v>
       </c>
       <c r="P2" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="Q2" t="n">
         <v>6</v>
       </c>
       <c r="R2" t="n">
-        <v>-19.35</v>
+        <v>-19.72</v>
       </c>
       <c r="S2" t="n">
-        <v>-12.9</v>
+        <v>-13.15</v>
       </c>
       <c r="T2" t="n">
         <v>1.8</v>
@@ -676,20 +676,20 @@
         <v>18</v>
       </c>
       <c r="W2" t="n">
-        <v>598.71</v>
+        <v>598.3099999999999</v>
       </c>
       <c r="X2" t="n">
-        <v>-7.29</v>
+        <v>-7.69</v>
       </c>
       <c r="Y2" t="n">
-        <v>2105.32</v>
+        <v>2104.87</v>
       </c>
       <c r="Z2" t="n">
-        <v>149.32</v>
+        <v>148.87</v>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>Laterale</t>
+          <t>Pressione breve</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -729,7 +729,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>2026-09-10T23:40:25+02:00</t>
+          <t>2026-09-11T14:14:10+02:00</t>
         </is>
       </c>
     </row>
@@ -770,7 +770,7 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
@@ -785,13 +785,13 @@
         <v>150</v>
       </c>
       <c r="M3" t="n">
-        <v>150.43</v>
+        <v>151.47</v>
       </c>
       <c r="N3" t="n">
-        <v>150.43</v>
+        <v>151.47</v>
       </c>
       <c r="O3" t="n">
-        <v>0.44</v>
+        <v>1.49</v>
       </c>
       <c r="P3" t="n">
         <v>0.01</v>
@@ -800,31 +800,31 @@
         <v>6</v>
       </c>
       <c r="R3" t="n">
-        <v>-5.57</v>
+        <v>-4.53</v>
       </c>
       <c r="S3" t="n">
-        <v>-3.71</v>
+        <v>-3.02</v>
       </c>
       <c r="T3" t="n">
         <v>0.3</v>
       </c>
       <c r="U3" t="n">
-        <v>3.17</v>
+        <v>3.76</v>
       </c>
       <c r="V3" t="n">
-        <v>13.29</v>
+        <v>15.9</v>
       </c>
       <c r="W3" t="n">
-        <v>609.92</v>
+        <v>612.76</v>
       </c>
       <c r="X3" t="n">
-        <v>3.92</v>
+        <v>6.76</v>
       </c>
       <c r="Y3" t="n">
-        <v>2077.61</v>
+        <v>2103.28</v>
       </c>
       <c r="Z3" t="n">
-        <v>121.61</v>
+        <v>147.28</v>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
@@ -868,7 +868,7 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>2026-09-10T23:40:25+02:00</t>
+          <t>2026-09-11T14:14:10+02:00</t>
         </is>
       </c>
     </row>
@@ -909,7 +909,7 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I4" t="n">
         <v>5000</v>
@@ -924,46 +924,46 @@
         <v>5000</v>
       </c>
       <c r="M4" t="n">
-        <v>4949.27</v>
+        <v>4983.2</v>
       </c>
       <c r="N4" t="n">
-        <v>4949.27</v>
+        <v>4983.2</v>
       </c>
       <c r="O4" t="n">
-        <v>-46.07</v>
+        <v>-11.67</v>
       </c>
       <c r="P4" t="n">
-        <v>4.66</v>
+        <v>5.12</v>
       </c>
       <c r="Q4" t="n">
         <v>6</v>
       </c>
       <c r="R4" t="n">
-        <v>-56.73</v>
+        <v>-22.8</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.13</v>
+        <v>-0.46</v>
       </c>
       <c r="T4" t="n">
         <v>3.4</v>
       </c>
       <c r="U4" t="n">
-        <v>2.19</v>
+        <v>2.68</v>
       </c>
       <c r="V4" t="n">
-        <v>9.039999999999999</v>
+        <v>11.14</v>
       </c>
       <c r="W4" t="n">
-        <v>5057.49</v>
+        <v>5116.59</v>
       </c>
       <c r="X4" t="n">
-        <v>51.49</v>
+        <v>110.59</v>
       </c>
       <c r="Y4" t="n">
-        <v>5396.56</v>
+        <v>5538.53</v>
       </c>
       <c r="Z4" t="n">
-        <v>390.56</v>
+        <v>532.53</v>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
@@ -1007,7 +1007,7 @@
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>2026-09-10T23:40:25+02:00</t>
+          <t>2026-09-11T14:14:10+02:00</t>
         </is>
       </c>
     </row>
@@ -1048,7 +1048,7 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I5" t="n">
         <v>5000</v>
@@ -1063,46 +1063,46 @@
         <v>5000</v>
       </c>
       <c r="M5" t="n">
-        <v>4944.46</v>
+        <v>4977.4</v>
       </c>
       <c r="N5" t="n">
-        <v>4944.46</v>
+        <v>4977.4</v>
       </c>
       <c r="O5" t="n">
-        <v>-53.64</v>
+        <v>-20.51</v>
       </c>
       <c r="P5" t="n">
-        <v>1.9</v>
+        <v>2.09</v>
       </c>
       <c r="Q5" t="n">
         <v>6</v>
       </c>
       <c r="R5" t="n">
-        <v>-61.54</v>
+        <v>-28.6</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.23</v>
+        <v>-0.57</v>
       </c>
       <c r="T5" t="n">
         <v>1.39</v>
       </c>
       <c r="U5" t="n">
-        <v>0.67</v>
+        <v>1.03</v>
       </c>
       <c r="V5" t="n">
-        <v>2.71</v>
+        <v>4.19</v>
       </c>
       <c r="W5" t="n">
-        <v>4977.62</v>
+        <v>5028.8</v>
       </c>
       <c r="X5" t="n">
-        <v>-28.38</v>
+        <v>22.8</v>
       </c>
       <c r="Y5" t="n">
-        <v>5078.45</v>
+        <v>5186.19</v>
       </c>
       <c r="Z5" t="n">
-        <v>72.45</v>
+        <v>180.19</v>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
@@ -1146,7 +1146,7 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>2026-09-10T23:40:25+02:00</t>
+          <t>2026-09-11T14:14:10+02:00</t>
         </is>
       </c>
     </row>
@@ -1187,7 +1187,7 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I6" t="n">
         <v>5000</v>
@@ -1202,46 +1202,46 @@
         <v>5000</v>
       </c>
       <c r="M6" t="n">
-        <v>4944.46</v>
+        <v>4977.4</v>
       </c>
       <c r="N6" t="n">
-        <v>4944.46</v>
+        <v>4977.4</v>
       </c>
       <c r="O6" t="n">
-        <v>-53.64</v>
+        <v>-20.51</v>
       </c>
       <c r="P6" t="n">
-        <v>1.9</v>
+        <v>2.09</v>
       </c>
       <c r="Q6" t="n">
         <v>6</v>
       </c>
       <c r="R6" t="n">
-        <v>-61.54</v>
+        <v>-28.6</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.23</v>
+        <v>-0.57</v>
       </c>
       <c r="T6" t="n">
         <v>1.39</v>
       </c>
       <c r="U6" t="n">
-        <v>0.67</v>
+        <v>1.03</v>
       </c>
       <c r="V6" t="n">
-        <v>2.71</v>
+        <v>4.19</v>
       </c>
       <c r="W6" t="n">
-        <v>4977.62</v>
+        <v>5028.8</v>
       </c>
       <c r="X6" t="n">
-        <v>-28.38</v>
+        <v>22.8</v>
       </c>
       <c r="Y6" t="n">
-        <v>5078.45</v>
+        <v>5186.19</v>
       </c>
       <c r="Z6" t="n">
-        <v>72.45</v>
+        <v>180.19</v>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
@@ -1285,7 +1285,7 @@
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>2026-09-10T23:40:25+02:00</t>
+          <t>2026-09-11T14:14:10+02:00</t>
         </is>
       </c>
     </row>
@@ -1326,7 +1326,7 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I7" t="n">
         <v>5000</v>
@@ -1341,46 +1341,46 @@
         <v>5000</v>
       </c>
       <c r="M7" t="n">
-        <v>4944.46</v>
+        <v>4977.4</v>
       </c>
       <c r="N7" t="n">
-        <v>4944.46</v>
+        <v>4977.4</v>
       </c>
       <c r="O7" t="n">
-        <v>-53.64</v>
+        <v>-20.51</v>
       </c>
       <c r="P7" t="n">
-        <v>1.9</v>
+        <v>2.09</v>
       </c>
       <c r="Q7" t="n">
         <v>6</v>
       </c>
       <c r="R7" t="n">
-        <v>-61.54</v>
+        <v>-28.6</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.23</v>
+        <v>-0.57</v>
       </c>
       <c r="T7" t="n">
         <v>1.39</v>
       </c>
       <c r="U7" t="n">
-        <v>0.67</v>
+        <v>1.03</v>
       </c>
       <c r="V7" t="n">
-        <v>2.71</v>
+        <v>4.19</v>
       </c>
       <c r="W7" t="n">
-        <v>4977.62</v>
+        <v>5028.8</v>
       </c>
       <c r="X7" t="n">
-        <v>-28.38</v>
+        <v>22.8</v>
       </c>
       <c r="Y7" t="n">
-        <v>5078.45</v>
+        <v>5186.19</v>
       </c>
       <c r="Z7" t="n">
-        <v>72.45</v>
+        <v>180.19</v>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
@@ -1424,7 +1424,7 @@
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>2026-09-10T23:40:25+02:00</t>
+          <t>2026-09-11T14:14:10+02:00</t>
         </is>
       </c>
     </row>
@@ -1465,7 +1465,7 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I8" t="n">
         <v>5000</v>
@@ -1480,46 +1480,46 @@
         <v>5000</v>
       </c>
       <c r="M8" t="n">
-        <v>4885.69</v>
+        <v>4915.66</v>
       </c>
       <c r="N8" t="n">
-        <v>4885.69</v>
+        <v>4915.66</v>
       </c>
       <c r="O8" t="n">
-        <v>-113.9</v>
+        <v>-83.88</v>
       </c>
       <c r="P8" t="n">
-        <v>0.41</v>
+        <v>0.45</v>
       </c>
       <c r="Q8" t="n">
         <v>6</v>
       </c>
       <c r="R8" t="n">
-        <v>-120.31</v>
+        <v>-90.34</v>
       </c>
       <c r="S8" t="n">
-        <v>-2.41</v>
+        <v>-1.81</v>
       </c>
       <c r="T8" t="n">
         <v>0.3</v>
       </c>
       <c r="U8" t="n">
-        <v>0.18</v>
+        <v>0.62</v>
       </c>
       <c r="V8" t="n">
-        <v>0.71</v>
+        <v>2.49</v>
       </c>
       <c r="W8" t="n">
-        <v>4894.36</v>
+        <v>4945.94</v>
       </c>
       <c r="X8" t="n">
-        <v>-111.64</v>
+        <v>-60.06</v>
       </c>
       <c r="Y8" t="n">
-        <v>4920.46</v>
+        <v>5037.88</v>
       </c>
       <c r="Z8" t="n">
-        <v>-85.54000000000001</v>
+        <v>31.88</v>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
@@ -1563,7 +1563,7 @@
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>2026-09-10T23:40:25+02:00</t>
+          <t>2026-09-11T14:14:10+02:00</t>
         </is>
       </c>
     </row>
@@ -1671,17 +1671,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-10T23:40:25+02:00</t>
+          <t>2026-09-11T14:14:10+02:00</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -1694,22 +1694,22 @@
         <v>25300</v>
       </c>
       <c r="H2" t="n">
-        <v>24955.42</v>
+        <v>25118.81</v>
       </c>
       <c r="I2" t="n">
-        <v>24955.42</v>
+        <v>25118.81</v>
       </c>
       <c r="J2" t="n">
-        <v>-386.58</v>
+        <v>-223.19</v>
       </c>
       <c r="K2" t="n">
-        <v>-1.53</v>
+        <v>-0.88</v>
       </c>
       <c r="L2" t="n">
-        <v>26093.34</v>
+        <v>26360</v>
       </c>
       <c r="M2" t="n">
-        <v>29735.3</v>
+        <v>30343.13</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>

--- a/AlphaForge_Fineco_Decision_Cockpit.xlsx
+++ b/AlphaForge_Fineco_Decision_Cockpit.xlsx
@@ -646,13 +646,13 @@
         <v>150</v>
       </c>
       <c r="M2" t="n">
-        <v>136.28</v>
+        <v>135.99</v>
       </c>
       <c r="N2" t="n">
-        <v>136.28</v>
+        <v>135.99</v>
       </c>
       <c r="O2" t="n">
-        <v>-13.64</v>
+        <v>-13.93</v>
       </c>
       <c r="P2" t="n">
         <v>0.08</v>
@@ -661,10 +661,10 @@
         <v>6</v>
       </c>
       <c r="R2" t="n">
-        <v>-19.72</v>
+        <v>-20.01</v>
       </c>
       <c r="S2" t="n">
-        <v>-13.15</v>
+        <v>-13.34</v>
       </c>
       <c r="T2" t="n">
         <v>1.8</v>
@@ -676,16 +676,16 @@
         <v>18</v>
       </c>
       <c r="W2" t="n">
-        <v>598.3099999999999</v>
+        <v>598.01</v>
       </c>
       <c r="X2" t="n">
-        <v>-7.69</v>
+        <v>-7.99</v>
       </c>
       <c r="Y2" t="n">
-        <v>2104.87</v>
+        <v>2104.53</v>
       </c>
       <c r="Z2" t="n">
-        <v>148.87</v>
+        <v>148.53</v>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
@@ -729,7 +729,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>2026-09-11T14:14:10+02:00</t>
+          <t>2026-09-11T16:29:34+02:00</t>
         </is>
       </c>
     </row>
@@ -785,13 +785,13 @@
         <v>150</v>
       </c>
       <c r="M3" t="n">
-        <v>151.47</v>
+        <v>151.46</v>
       </c>
       <c r="N3" t="n">
-        <v>151.47</v>
+        <v>151.46</v>
       </c>
       <c r="O3" t="n">
-        <v>1.49</v>
+        <v>1.47</v>
       </c>
       <c r="P3" t="n">
         <v>0.01</v>
@@ -800,31 +800,31 @@
         <v>6</v>
       </c>
       <c r="R3" t="n">
-        <v>-4.53</v>
+        <v>-4.54</v>
       </c>
       <c r="S3" t="n">
-        <v>-3.02</v>
+        <v>-3.03</v>
       </c>
       <c r="T3" t="n">
         <v>0.3</v>
       </c>
       <c r="U3" t="n">
-        <v>3.76</v>
+        <v>3.75</v>
       </c>
       <c r="V3" t="n">
-        <v>15.9</v>
+        <v>15.86</v>
       </c>
       <c r="W3" t="n">
-        <v>612.76</v>
+        <v>612.71</v>
       </c>
       <c r="X3" t="n">
-        <v>6.76</v>
+        <v>6.71</v>
       </c>
       <c r="Y3" t="n">
-        <v>2103.28</v>
+        <v>2102.84</v>
       </c>
       <c r="Z3" t="n">
-        <v>147.28</v>
+        <v>146.84</v>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
@@ -868,7 +868,7 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>2026-09-11T14:14:10+02:00</t>
+          <t>2026-09-11T16:29:34+02:00</t>
         </is>
       </c>
     </row>
@@ -924,13 +924,13 @@
         <v>5000</v>
       </c>
       <c r="M4" t="n">
-        <v>4983.2</v>
+        <v>4991.19</v>
       </c>
       <c r="N4" t="n">
-        <v>4983.2</v>
+        <v>4991.19</v>
       </c>
       <c r="O4" t="n">
-        <v>-11.67</v>
+        <v>-3.69</v>
       </c>
       <c r="P4" t="n">
         <v>5.12</v>
@@ -939,31 +939,31 @@
         <v>6</v>
       </c>
       <c r="R4" t="n">
-        <v>-22.8</v>
+        <v>-14.81</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.46</v>
+        <v>-0.3</v>
       </c>
       <c r="T4" t="n">
         <v>3.4</v>
       </c>
       <c r="U4" t="n">
-        <v>2.68</v>
+        <v>2.83</v>
       </c>
       <c r="V4" t="n">
-        <v>11.14</v>
+        <v>11.82</v>
       </c>
       <c r="W4" t="n">
-        <v>5116.59</v>
+        <v>5132.6</v>
       </c>
       <c r="X4" t="n">
-        <v>110.59</v>
+        <v>126.6</v>
       </c>
       <c r="Y4" t="n">
-        <v>5538.53</v>
+        <v>5581.34</v>
       </c>
       <c r="Z4" t="n">
-        <v>532.53</v>
+        <v>575.34</v>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
@@ -1007,7 +1007,7 @@
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>2026-09-11T14:14:10+02:00</t>
+          <t>2026-09-11T16:29:34+02:00</t>
         </is>
       </c>
     </row>
@@ -1063,13 +1063,13 @@
         <v>5000</v>
       </c>
       <c r="M5" t="n">
-        <v>4977.4</v>
+        <v>4986.86</v>
       </c>
       <c r="N5" t="n">
-        <v>4977.4</v>
+        <v>4986.86</v>
       </c>
       <c r="O5" t="n">
-        <v>-20.51</v>
+        <v>-11.04</v>
       </c>
       <c r="P5" t="n">
         <v>2.09</v>
@@ -1078,31 +1078,31 @@
         <v>6</v>
       </c>
       <c r="R5" t="n">
-        <v>-28.6</v>
+        <v>-19.14</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.57</v>
+        <v>-0.38</v>
       </c>
       <c r="T5" t="n">
         <v>1.39</v>
       </c>
       <c r="U5" t="n">
-        <v>1.03</v>
+        <v>1.22</v>
       </c>
       <c r="V5" t="n">
-        <v>4.19</v>
+        <v>4.98</v>
       </c>
       <c r="W5" t="n">
-        <v>5028.8</v>
+        <v>5047.88</v>
       </c>
       <c r="X5" t="n">
-        <v>22.8</v>
+        <v>41.88</v>
       </c>
       <c r="Y5" t="n">
-        <v>5186.19</v>
+        <v>5235.45</v>
       </c>
       <c r="Z5" t="n">
-        <v>180.19</v>
+        <v>229.45</v>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
@@ -1146,7 +1146,7 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>2026-09-11T14:14:10+02:00</t>
+          <t>2026-09-11T16:29:34+02:00</t>
         </is>
       </c>
     </row>
@@ -1202,13 +1202,13 @@
         <v>5000</v>
       </c>
       <c r="M6" t="n">
-        <v>4977.4</v>
+        <v>4986.86</v>
       </c>
       <c r="N6" t="n">
-        <v>4977.4</v>
+        <v>4986.86</v>
       </c>
       <c r="O6" t="n">
-        <v>-20.51</v>
+        <v>-11.04</v>
       </c>
       <c r="P6" t="n">
         <v>2.09</v>
@@ -1217,31 +1217,31 @@
         <v>6</v>
       </c>
       <c r="R6" t="n">
-        <v>-28.6</v>
+        <v>-19.14</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.57</v>
+        <v>-0.38</v>
       </c>
       <c r="T6" t="n">
         <v>1.39</v>
       </c>
       <c r="U6" t="n">
-        <v>1.03</v>
+        <v>1.22</v>
       </c>
       <c r="V6" t="n">
-        <v>4.19</v>
+        <v>4.98</v>
       </c>
       <c r="W6" t="n">
-        <v>5028.8</v>
+        <v>5047.88</v>
       </c>
       <c r="X6" t="n">
-        <v>22.8</v>
+        <v>41.88</v>
       </c>
       <c r="Y6" t="n">
-        <v>5186.19</v>
+        <v>5235.45</v>
       </c>
       <c r="Z6" t="n">
-        <v>180.19</v>
+        <v>229.45</v>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
@@ -1285,7 +1285,7 @@
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>2026-09-11T14:14:10+02:00</t>
+          <t>2026-09-11T16:29:34+02:00</t>
         </is>
       </c>
     </row>
@@ -1341,13 +1341,13 @@
         <v>5000</v>
       </c>
       <c r="M7" t="n">
-        <v>4977.4</v>
+        <v>4986.86</v>
       </c>
       <c r="N7" t="n">
-        <v>4977.4</v>
+        <v>4986.86</v>
       </c>
       <c r="O7" t="n">
-        <v>-20.51</v>
+        <v>-11.04</v>
       </c>
       <c r="P7" t="n">
         <v>2.09</v>
@@ -1356,31 +1356,31 @@
         <v>6</v>
       </c>
       <c r="R7" t="n">
-        <v>-28.6</v>
+        <v>-19.14</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.57</v>
+        <v>-0.38</v>
       </c>
       <c r="T7" t="n">
         <v>1.39</v>
       </c>
       <c r="U7" t="n">
-        <v>1.03</v>
+        <v>1.22</v>
       </c>
       <c r="V7" t="n">
-        <v>4.19</v>
+        <v>4.98</v>
       </c>
       <c r="W7" t="n">
-        <v>5028.8</v>
+        <v>5047.88</v>
       </c>
       <c r="X7" t="n">
-        <v>22.8</v>
+        <v>41.88</v>
       </c>
       <c r="Y7" t="n">
-        <v>5186.19</v>
+        <v>5235.45</v>
       </c>
       <c r="Z7" t="n">
-        <v>180.19</v>
+        <v>229.45</v>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
@@ -1424,7 +1424,7 @@
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>2026-09-11T14:14:10+02:00</t>
+          <t>2026-09-11T16:29:34+02:00</t>
         </is>
       </c>
     </row>
@@ -1480,13 +1480,13 @@
         <v>5000</v>
       </c>
       <c r="M8" t="n">
-        <v>4915.66</v>
+        <v>4910.28</v>
       </c>
       <c r="N8" t="n">
-        <v>4915.66</v>
+        <v>4910.28</v>
       </c>
       <c r="O8" t="n">
-        <v>-83.88</v>
+        <v>-89.27</v>
       </c>
       <c r="P8" t="n">
         <v>0.45</v>
@@ -1495,31 +1495,31 @@
         <v>6</v>
       </c>
       <c r="R8" t="n">
-        <v>-90.34</v>
+        <v>-95.72</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.81</v>
+        <v>-1.91</v>
       </c>
       <c r="T8" t="n">
         <v>0.3</v>
       </c>
       <c r="U8" t="n">
-        <v>0.62</v>
+        <v>0.5</v>
       </c>
       <c r="V8" t="n">
-        <v>2.49</v>
+        <v>2.03</v>
       </c>
       <c r="W8" t="n">
-        <v>4945.94</v>
+        <v>4935.06</v>
       </c>
       <c r="X8" t="n">
-        <v>-60.06</v>
+        <v>-70.94</v>
       </c>
       <c r="Y8" t="n">
-        <v>5037.88</v>
+        <v>5010.15</v>
       </c>
       <c r="Z8" t="n">
-        <v>31.88</v>
+        <v>4.15</v>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
@@ -1563,7 +1563,7 @@
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>2026-09-11T14:14:10+02:00</t>
+          <t>2026-09-11T16:29:34+02:00</t>
         </is>
       </c>
     </row>
@@ -1671,7 +1671,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-11T14:14:10+02:00</t>
+          <t>2026-09-11T16:29:34+02:00</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1694,22 +1694,22 @@
         <v>25300</v>
       </c>
       <c r="H2" t="n">
-        <v>25118.81</v>
+        <v>25149.5</v>
       </c>
       <c r="I2" t="n">
-        <v>25118.81</v>
+        <v>25149.5</v>
       </c>
       <c r="J2" t="n">
-        <v>-223.19</v>
+        <v>-192.5</v>
       </c>
       <c r="K2" t="n">
-        <v>-0.88</v>
+        <v>-0.76</v>
       </c>
       <c r="L2" t="n">
-        <v>26360</v>
+        <v>26422.02</v>
       </c>
       <c r="M2" t="n">
-        <v>30343.13</v>
+        <v>30505.21</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>

--- a/AlphaForge_Fineco_Decision_Cockpit.xlsx
+++ b/AlphaForge_Fineco_Decision_Cockpit.xlsx
@@ -646,13 +646,13 @@
         <v>150</v>
       </c>
       <c r="M2" t="n">
-        <v>135.99</v>
+        <v>135.1</v>
       </c>
       <c r="N2" t="n">
-        <v>135.99</v>
+        <v>135.1</v>
       </c>
       <c r="O2" t="n">
-        <v>-13.93</v>
+        <v>-14.82</v>
       </c>
       <c r="P2" t="n">
         <v>0.08</v>
@@ -661,10 +661,10 @@
         <v>6</v>
       </c>
       <c r="R2" t="n">
-        <v>-20.01</v>
+        <v>-20.9</v>
       </c>
       <c r="S2" t="n">
-        <v>-13.34</v>
+        <v>-13.93</v>
       </c>
       <c r="T2" t="n">
         <v>1.8</v>
@@ -676,16 +676,16 @@
         <v>18</v>
       </c>
       <c r="W2" t="n">
-        <v>598.01</v>
+        <v>597.09</v>
       </c>
       <c r="X2" t="n">
-        <v>-7.99</v>
+        <v>-8.91</v>
       </c>
       <c r="Y2" t="n">
-        <v>2104.53</v>
+        <v>2103.48</v>
       </c>
       <c r="Z2" t="n">
-        <v>148.53</v>
+        <v>147.48</v>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
@@ -729,7 +729,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>2026-09-11T16:29:34+02:00</t>
+          <t>2026-09-11T19:02:13+02:00</t>
         </is>
       </c>
     </row>
@@ -785,13 +785,13 @@
         <v>150</v>
       </c>
       <c r="M3" t="n">
-        <v>151.46</v>
+        <v>152.03</v>
       </c>
       <c r="N3" t="n">
-        <v>151.46</v>
+        <v>152.03</v>
       </c>
       <c r="O3" t="n">
-        <v>1.47</v>
+        <v>2.04</v>
       </c>
       <c r="P3" t="n">
         <v>0.01</v>
@@ -800,31 +800,31 @@
         <v>6</v>
       </c>
       <c r="R3" t="n">
-        <v>-4.54</v>
+        <v>-3.97</v>
       </c>
       <c r="S3" t="n">
-        <v>-3.03</v>
+        <v>-2.65</v>
       </c>
       <c r="T3" t="n">
         <v>0.3</v>
       </c>
       <c r="U3" t="n">
-        <v>3.75</v>
+        <v>4.11</v>
       </c>
       <c r="V3" t="n">
-        <v>15.86</v>
+        <v>17.46</v>
       </c>
       <c r="W3" t="n">
-        <v>612.71</v>
+        <v>614.37</v>
       </c>
       <c r="X3" t="n">
-        <v>6.71</v>
+        <v>8.369999999999999</v>
       </c>
       <c r="Y3" t="n">
-        <v>2102.84</v>
+        <v>2118.46</v>
       </c>
       <c r="Z3" t="n">
-        <v>146.84</v>
+        <v>162.46</v>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
@@ -868,7 +868,7 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>2026-09-11T16:29:34+02:00</t>
+          <t>2026-09-11T19:02:13+02:00</t>
         </is>
       </c>
     </row>
@@ -924,13 +924,13 @@
         <v>5000</v>
       </c>
       <c r="M4" t="n">
-        <v>4991.19</v>
+        <v>4987.5</v>
       </c>
       <c r="N4" t="n">
-        <v>4991.19</v>
+        <v>4987.5</v>
       </c>
       <c r="O4" t="n">
-        <v>-3.69</v>
+        <v>-7.37</v>
       </c>
       <c r="P4" t="n">
         <v>5.12</v>
@@ -939,31 +939,31 @@
         <v>6</v>
       </c>
       <c r="R4" t="n">
-        <v>-14.81</v>
+        <v>-18.5</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.3</v>
+        <v>-0.37</v>
       </c>
       <c r="T4" t="n">
         <v>3.4</v>
       </c>
       <c r="U4" t="n">
-        <v>2.83</v>
+        <v>2.76</v>
       </c>
       <c r="V4" t="n">
-        <v>11.82</v>
+        <v>11.51</v>
       </c>
       <c r="W4" t="n">
-        <v>5132.6</v>
+        <v>5125.21</v>
       </c>
       <c r="X4" t="n">
-        <v>126.6</v>
+        <v>119.21</v>
       </c>
       <c r="Y4" t="n">
-        <v>5581.34</v>
+        <v>5561.57</v>
       </c>
       <c r="Z4" t="n">
-        <v>575.34</v>
+        <v>555.5700000000001</v>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
@@ -1007,7 +1007,7 @@
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>2026-09-11T16:29:34+02:00</t>
+          <t>2026-09-11T19:02:13+02:00</t>
         </is>
       </c>
     </row>
@@ -1063,13 +1063,13 @@
         <v>5000</v>
       </c>
       <c r="M5" t="n">
-        <v>4986.86</v>
+        <v>4992.38</v>
       </c>
       <c r="N5" t="n">
-        <v>4986.86</v>
+        <v>4992.38</v>
       </c>
       <c r="O5" t="n">
-        <v>-11.04</v>
+        <v>-5.52</v>
       </c>
       <c r="P5" t="n">
         <v>2.09</v>
@@ -1078,31 +1078,31 @@
         <v>6</v>
       </c>
       <c r="R5" t="n">
-        <v>-19.14</v>
+        <v>-13.62</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.38</v>
+        <v>-0.27</v>
       </c>
       <c r="T5" t="n">
         <v>1.39</v>
       </c>
       <c r="U5" t="n">
-        <v>1.22</v>
+        <v>1.33</v>
       </c>
       <c r="V5" t="n">
-        <v>4.98</v>
+        <v>5.45</v>
       </c>
       <c r="W5" t="n">
-        <v>5047.88</v>
+        <v>5059.01</v>
       </c>
       <c r="X5" t="n">
-        <v>41.88</v>
+        <v>53.01</v>
       </c>
       <c r="Y5" t="n">
-        <v>5235.45</v>
+        <v>5264.25</v>
       </c>
       <c r="Z5" t="n">
-        <v>229.45</v>
+        <v>258.25</v>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
@@ -1146,7 +1146,7 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>2026-09-11T16:29:34+02:00</t>
+          <t>2026-09-11T19:02:13+02:00</t>
         </is>
       </c>
     </row>
@@ -1202,13 +1202,13 @@
         <v>5000</v>
       </c>
       <c r="M6" t="n">
-        <v>4986.86</v>
+        <v>4992.38</v>
       </c>
       <c r="N6" t="n">
-        <v>4986.86</v>
+        <v>4992.38</v>
       </c>
       <c r="O6" t="n">
-        <v>-11.04</v>
+        <v>-5.52</v>
       </c>
       <c r="P6" t="n">
         <v>2.09</v>
@@ -1217,31 +1217,31 @@
         <v>6</v>
       </c>
       <c r="R6" t="n">
-        <v>-19.14</v>
+        <v>-13.62</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.38</v>
+        <v>-0.27</v>
       </c>
       <c r="T6" t="n">
         <v>1.39</v>
       </c>
       <c r="U6" t="n">
-        <v>1.22</v>
+        <v>1.33</v>
       </c>
       <c r="V6" t="n">
-        <v>4.98</v>
+        <v>5.45</v>
       </c>
       <c r="W6" t="n">
-        <v>5047.88</v>
+        <v>5059.01</v>
       </c>
       <c r="X6" t="n">
-        <v>41.88</v>
+        <v>53.01</v>
       </c>
       <c r="Y6" t="n">
-        <v>5235.45</v>
+        <v>5264.25</v>
       </c>
       <c r="Z6" t="n">
-        <v>229.45</v>
+        <v>258.25</v>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
@@ -1285,7 +1285,7 @@
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>2026-09-11T16:29:34+02:00</t>
+          <t>2026-09-11T19:02:13+02:00</t>
         </is>
       </c>
     </row>
@@ -1341,13 +1341,13 @@
         <v>5000</v>
       </c>
       <c r="M7" t="n">
-        <v>4986.86</v>
+        <v>4992.38</v>
       </c>
       <c r="N7" t="n">
-        <v>4986.86</v>
+        <v>4992.38</v>
       </c>
       <c r="O7" t="n">
-        <v>-11.04</v>
+        <v>-5.52</v>
       </c>
       <c r="P7" t="n">
         <v>2.09</v>
@@ -1356,31 +1356,31 @@
         <v>6</v>
       </c>
       <c r="R7" t="n">
-        <v>-19.14</v>
+        <v>-13.62</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.38</v>
+        <v>-0.27</v>
       </c>
       <c r="T7" t="n">
         <v>1.39</v>
       </c>
       <c r="U7" t="n">
-        <v>1.22</v>
+        <v>1.33</v>
       </c>
       <c r="V7" t="n">
-        <v>4.98</v>
+        <v>5.45</v>
       </c>
       <c r="W7" t="n">
-        <v>5047.88</v>
+        <v>5059.01</v>
       </c>
       <c r="X7" t="n">
-        <v>41.88</v>
+        <v>53.01</v>
       </c>
       <c r="Y7" t="n">
-        <v>5235.45</v>
+        <v>5264.25</v>
       </c>
       <c r="Z7" t="n">
-        <v>229.45</v>
+        <v>258.25</v>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
@@ -1424,7 +1424,7 @@
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>2026-09-11T16:29:34+02:00</t>
+          <t>2026-09-11T19:02:13+02:00</t>
         </is>
       </c>
     </row>
@@ -1480,13 +1480,13 @@
         <v>5000</v>
       </c>
       <c r="M8" t="n">
-        <v>4910.28</v>
+        <v>4914.12</v>
       </c>
       <c r="N8" t="n">
-        <v>4910.28</v>
+        <v>4914.12</v>
       </c>
       <c r="O8" t="n">
-        <v>-89.27</v>
+        <v>-85.42</v>
       </c>
       <c r="P8" t="n">
         <v>0.45</v>
@@ -1495,31 +1495,31 @@
         <v>6</v>
       </c>
       <c r="R8" t="n">
-        <v>-95.72</v>
+        <v>-91.88</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.91</v>
+        <v>-1.84</v>
       </c>
       <c r="T8" t="n">
         <v>0.3</v>
       </c>
       <c r="U8" t="n">
-        <v>0.5</v>
+        <v>0.58</v>
       </c>
       <c r="V8" t="n">
-        <v>2.03</v>
+        <v>2.36</v>
       </c>
       <c r="W8" t="n">
-        <v>4935.06</v>
+        <v>4942.83</v>
       </c>
       <c r="X8" t="n">
-        <v>-70.94</v>
+        <v>-63.17</v>
       </c>
       <c r="Y8" t="n">
-        <v>5010.15</v>
+        <v>5029.95</v>
       </c>
       <c r="Z8" t="n">
-        <v>4.15</v>
+        <v>23.95</v>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
@@ -1563,7 +1563,7 @@
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>2026-09-11T16:29:34+02:00</t>
+          <t>2026-09-11T19:02:13+02:00</t>
         </is>
       </c>
     </row>
@@ -1671,7 +1671,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-11T16:29:34+02:00</t>
+          <t>2026-09-11T19:02:13+02:00</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1694,22 +1694,22 @@
         <v>25300</v>
       </c>
       <c r="H2" t="n">
-        <v>25149.5</v>
+        <v>25165.89</v>
       </c>
       <c r="I2" t="n">
-        <v>25149.5</v>
+        <v>25165.89</v>
       </c>
       <c r="J2" t="n">
-        <v>-192.5</v>
+        <v>-176.11</v>
       </c>
       <c r="K2" t="n">
-        <v>-0.76</v>
+        <v>-0.7</v>
       </c>
       <c r="L2" t="n">
-        <v>26422.02</v>
+        <v>26456.53</v>
       </c>
       <c r="M2" t="n">
-        <v>30505.21</v>
+        <v>30606.21</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>

--- a/AlphaForge_Fineco_Decision_Cockpit.xlsx
+++ b/AlphaForge_Fineco_Decision_Cockpit.xlsx
@@ -729,7 +729,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>2026-09-11T19:02:13+02:00</t>
+          <t>2026-09-11T21:10:06+02:00</t>
         </is>
       </c>
     </row>
@@ -868,7 +868,7 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>2026-09-11T19:02:13+02:00</t>
+          <t>2026-09-11T21:10:06+02:00</t>
         </is>
       </c>
     </row>
@@ -1007,7 +1007,7 @@
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>2026-09-11T19:02:13+02:00</t>
+          <t>2026-09-11T21:10:06+02:00</t>
         </is>
       </c>
     </row>
@@ -1146,7 +1146,7 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>2026-09-11T19:02:13+02:00</t>
+          <t>2026-09-11T21:10:06+02:00</t>
         </is>
       </c>
     </row>
@@ -1285,7 +1285,7 @@
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>2026-09-11T19:02:13+02:00</t>
+          <t>2026-09-11T21:10:06+02:00</t>
         </is>
       </c>
     </row>
@@ -1424,7 +1424,7 @@
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>2026-09-11T19:02:13+02:00</t>
+          <t>2026-09-11T21:10:06+02:00</t>
         </is>
       </c>
     </row>
@@ -1563,7 +1563,7 @@
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>2026-09-11T19:02:13+02:00</t>
+          <t>2026-09-11T21:10:06+02:00</t>
         </is>
       </c>
     </row>
@@ -1671,7 +1671,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-11T19:02:13+02:00</t>
+          <t>2026-09-11T21:10:06+02:00</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">

--- a/AlphaForge_Fineco_Decision_Cockpit.xlsx
+++ b/AlphaForge_Fineco_Decision_Cockpit.xlsx
@@ -729,7 +729,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>2026-09-11T21:10:06+02:00</t>
+          <t>2026-09-11T23:45:23+02:00</t>
         </is>
       </c>
     </row>
@@ -868,7 +868,7 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>2026-09-11T21:10:06+02:00</t>
+          <t>2026-09-11T23:45:23+02:00</t>
         </is>
       </c>
     </row>
@@ -1007,7 +1007,7 @@
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>2026-09-11T21:10:06+02:00</t>
+          <t>2026-09-11T23:45:23+02:00</t>
         </is>
       </c>
     </row>
@@ -1146,7 +1146,7 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>2026-09-11T21:10:06+02:00</t>
+          <t>2026-09-11T23:45:23+02:00</t>
         </is>
       </c>
     </row>
@@ -1285,7 +1285,7 @@
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>2026-09-11T21:10:06+02:00</t>
+          <t>2026-09-11T23:45:23+02:00</t>
         </is>
       </c>
     </row>
@@ -1424,7 +1424,7 @@
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>2026-09-11T21:10:06+02:00</t>
+          <t>2026-09-11T23:45:23+02:00</t>
         </is>
       </c>
     </row>
@@ -1563,7 +1563,7 @@
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>2026-09-11T21:10:06+02:00</t>
+          <t>2026-09-11T23:45:23+02:00</t>
         </is>
       </c>
     </row>
@@ -1671,7 +1671,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-11T21:10:06+02:00</t>
+          <t>2026-09-11T23:45:23+02:00</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
